--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1012F03-171A-405B-9C4C-D93912EEA93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0976D211-EC5B-4FB0-B4E4-EBBF92300B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
-    <sheet name="Main" sheetId="2" r:id="rId2"/>
+    <sheet name="AudioMetadata" sheetId="3" r:id="rId2"/>
+    <sheet name="AudioPlaylist" sheetId="4" r:id="rId3"/>
+    <sheet name="AudioNormalization" sheetId="5" r:id="rId4"/>
+    <sheet name="DirectoryProcessing" sheetId="6" r:id="rId5"/>
+    <sheet name="SubprocessUtilities" sheetId="7" r:id="rId6"/>
+    <sheet name="Main" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,50 +40,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="70">
   <si>
     <t>package</t>
   </si>
   <si>
-    <t>audio_info</t>
-  </si>
-  <si>
-    <t>Test Needed</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>audio_art.py</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>AudioArt</t>
-  </si>
-  <si>
-    <t>Instance defs</t>
-  </si>
-  <si>
     <t>__init__</t>
   </si>
   <si>
     <t>__unpack_asf_image</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>gets called by extract_asf_art</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>__write_data</t>
   </si>
   <si>
@@ -88,9 +63,6 @@
     <t>extract_album_art</t>
   </si>
   <si>
-    <t>YES</t>
-  </si>
-  <si>
     <t>extract_asf_art</t>
   </si>
   <si>
@@ -130,9 +102,6 @@
     <t>function</t>
   </si>
   <si>
-    <t>All Test Written</t>
-  </si>
-  <si>
     <t>extract art from asf/wma file</t>
   </si>
   <si>
@@ -142,9 +111,6 @@
     <t>extract art from valid audio file</t>
   </si>
   <si>
-    <t>Test_Crush-Live.mp3</t>
-  </si>
-  <si>
     <t>Billie Holdiay-Georgia On My Mind.wma</t>
   </si>
   <si>
@@ -157,9 +123,6 @@
     <t>test_extract_ffmpeg_art</t>
   </si>
   <si>
-    <t>all inputs reside in /tests and /tests/Music/</t>
-  </si>
-  <si>
     <t>test_extract_mp3_art</t>
   </si>
   <si>
@@ -202,18 +165,9 @@
     <t>test.m3u</t>
   </si>
   <si>
-    <t>extract art file folder.jpg already exists</t>
-  </si>
-  <si>
-    <t>extract art file input audio not m4a/mp3/wma</t>
-  </si>
-  <si>
     <t>ABBA-Waterloo.jpg</t>
   </si>
   <si>
-    <t>text_extract_album_art_invalid_audio</t>
-  </si>
-  <si>
     <t>comments</t>
   </si>
   <si>
@@ -226,14 +180,83 @@
     <t>ensure pri method fail and sec method passes</t>
   </si>
   <si>
-    <t>guard check</t>
+    <t>test needed</t>
+  </si>
+  <si>
+    <t>written</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>audio file has a video stream</t>
+  </si>
+  <si>
+    <t>audio file does not have video stream</t>
+  </si>
+  <si>
+    <t>test_has_video_stream_true</t>
+  </si>
+  <si>
+    <t>test_has_video_stream_false</t>
+  </si>
+  <si>
+    <t>Joshua Davis-Workingmans's Hymn.m4a</t>
+  </si>
+  <si>
+    <t>test_extract_ffmpeg_art_no_stream</t>
+  </si>
+  <si>
+    <t>extract art from valid audio file w/o stream</t>
+  </si>
+  <si>
+    <t>extract album art from file that already has co-located Folder.jpg file</t>
+  </si>
+  <si>
+    <t>extract album art from non-valid file</t>
+  </si>
+  <si>
+    <t>test_extract_album_art_invalid_audio</t>
+  </si>
+  <si>
+    <t>No_tag_Crush-Live.mp3</t>
+  </si>
+  <si>
+    <t>module</t>
+  </si>
+  <si>
+    <t>src.info</t>
+  </si>
+  <si>
+    <t>audio_art</t>
+  </si>
+  <si>
+    <t>test def</t>
+  </si>
+  <si>
+    <t>test inputs</t>
+  </si>
+  <si>
+    <t>in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
+  </si>
+  <si>
+    <t>set album art for album dirs, 1 Folder .jpg exists, 1 folder .jpg copied from AlbumArt, rest of albums no album art set</t>
+  </si>
+  <si>
+    <t>test_set_album_art</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,16 +270,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -264,16 +310,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,330 +719,492 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240D0244-C07C-4B0D-B34B-DEFFB8A00779}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="48" style="2" customWidth="1"/>
-    <col min="7" max="7" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G24">
+    <sortCondition ref="A6:A42"/>
+    <sortCondition ref="E6:E42"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B59A74-3B3D-46A0-BA00-4CC6B3EB725F}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D5" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G5" s="5" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D29" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -919,29 +1212,314 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98D598E5-EDEF-4045-9437-C9EF65D16CFD}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D531ACB7-E8E0-47CE-BF75-27CCC9C8A44A}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA201B6-2CF8-401F-BDC0-3BC1ADEB0E11}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A88A2F6-1FD2-41F2-BBD9-348C6590770F}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5ED90A-9D84-40F3-BE55-6E6A44BF6F1B}">
-  <dimension ref="B2:B5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C5" s="5" t="s">
         <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0976D211-EC5B-4FB0-B4E4-EBBF92300B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC8410-EC31-4D5B-A074-0385C7B3C30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="72">
   <si>
     <t>package</t>
   </si>
@@ -84,9 +84,6 @@
     <t>set_album_art</t>
   </si>
   <si>
-    <t>??</t>
-  </si>
-  <si>
     <t>extract art file w/o tags or stream</t>
   </si>
   <si>
@@ -250,6 +247,15 @@
   </si>
   <si>
     <t>test_set_album_art</t>
+  </si>
+  <si>
+    <t>the 3 typed extract functions cover most of this, except for a pattern valid/invalid test in main.py</t>
+  </si>
+  <si>
+    <t>test for extract walk valid/invalide pattern</t>
+  </si>
+  <si>
+    <t>audio_metadata</t>
   </si>
 </sst>
 </file>
@@ -373,13 +379,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -737,408 +742,416 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="E12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="16"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E24" s="1"/>
@@ -1171,40 +1184,48 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1233,37 +1254,36 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1292,37 +1312,36 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1351,37 +1370,36 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1410,37 +1428,36 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1450,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5ED90A-9D84-40F3-BE55-6E6A44BF6F1B}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -1469,57 +1486,61 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC8410-EC31-4D5B-A074-0385C7B3C30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE346F7-4387-4080-B3EA-703CBA3E39CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="139">
   <si>
     <t>package</t>
   </si>
@@ -256,6 +256,207 @@
   </si>
   <si>
     <t>audio_metadata</t>
+  </si>
+  <si>
+    <t>audio_playlist</t>
+  </si>
+  <si>
+    <t>src.audio_normalize</t>
+  </si>
+  <si>
+    <t>audio_normalization</t>
+  </si>
+  <si>
+    <t>src.dir_processing</t>
+  </si>
+  <si>
+    <t>directory_processing</t>
+  </si>
+  <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>subprocess_utilities</t>
+  </si>
+  <si>
+    <t>convert_file</t>
+  </si>
+  <si>
+    <t>convert_walk</t>
+  </si>
+  <si>
+    <t>create_album_dir</t>
+  </si>
+  <si>
+    <t>get_any_tags</t>
+  </si>
+  <si>
+    <t>get_m4a_tags</t>
+  </si>
+  <si>
+    <t>get_media_info</t>
+  </si>
+  <si>
+    <t>get_media_info_dict</t>
+  </si>
+  <si>
+    <t>get_media_info_walk</t>
+  </si>
+  <si>
+    <t>get_media_tags</t>
+  </si>
+  <si>
+    <t>get_metadata_type</t>
+  </si>
+  <si>
+    <t>get_mp3_tags</t>
+  </si>
+  <si>
+    <t>get_tags_walk</t>
+  </si>
+  <si>
+    <t>get_uniquie_media_keys</t>
+  </si>
+  <si>
+    <t>get_wma_tags</t>
+  </si>
+  <si>
+    <t>has_art_tag</t>
+  </si>
+  <si>
+    <t>load_any_file</t>
+  </si>
+  <si>
+    <t>load_m4a_file</t>
+  </si>
+  <si>
+    <t>load_mp3_file</t>
+  </si>
+  <si>
+    <t>load_wma_file</t>
+  </si>
+  <si>
+    <t>map_m4a_tags</t>
+  </si>
+  <si>
+    <t>map_mp3_tags</t>
+  </si>
+  <si>
+    <t>map_wma_tags</t>
+  </si>
+  <si>
+    <t>a pattern valid/invalid in main.py covers this function</t>
+  </si>
+  <si>
+    <t>calls load_any_file</t>
+  </si>
+  <si>
+    <t>call load_m4a_file</t>
+  </si>
+  <si>
+    <t>calls load_mp3_file</t>
+  </si>
+  <si>
+    <t>calls load_wma_file</t>
+  </si>
+  <si>
+    <t>do I even need this any more?? Should I output to file instead of console?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info. Best to just happy path test converting m4a, mp3, wma and verify output mp3 file has correct text metadata and has art  metadata </t>
+  </si>
+  <si>
+    <t>this function should be removed, it's just a wrapper for get_media_info_dict. Refactor as needed.</t>
+  </si>
+  <si>
+    <t>PITA to test, each os returns slightly diff dict, especially filename. Test return dict is not None, has keys/values and 2 inner dicts?</t>
+  </si>
+  <si>
+    <t>current media info dict tests is really just a TAGS inner dict test - which is the test for this function</t>
+  </si>
+  <si>
+    <t>calls get_media_tags OR get_metadata_type, then appropriate get_m4a/mp3/wma_tags. Also a pattern valid/invalid type.</t>
+  </si>
+  <si>
+    <t>calls get_media_tags. Very much a 1 off, maybe move to separate script? Could laso be converted to file output.</t>
+  </si>
+  <si>
+    <t>calls get_any_tags</t>
+  </si>
+  <si>
+    <t>not an audio file: m3u</t>
+  </si>
+  <si>
+    <t>with art tag: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>without art tag: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>add a valid audio file check to code</t>
+  </si>
+  <si>
+    <t>valid audio: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>invalid file type</t>
+  </si>
+  <si>
+    <t>wma</t>
+  </si>
+  <si>
+    <t>not wma</t>
+  </si>
+  <si>
+    <t>not mp3</t>
+  </si>
+  <si>
+    <t>mp3</t>
+  </si>
+  <si>
+    <t>not m4a</t>
+  </si>
+  <si>
+    <t>m4a</t>
+  </si>
+  <si>
+    <t>mp3 with metadata</t>
+  </si>
+  <si>
+    <t>mp3 w/o metadata</t>
+  </si>
+  <si>
+    <t>wma with metadata</t>
+  </si>
+  <si>
+    <t>m4a with metadata</t>
+  </si>
+  <si>
+    <t>m4a w/o metadata</t>
+  </si>
+  <si>
+    <t>valid audio w/ metadata: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>valid audio w/o metadata: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>wma w/o metadata</t>
+  </si>
+  <si>
+    <t>calls get_media_tags, make_album_dir, move_audio_file, create_csv. WILL modify /test/Music, which I do not want. Is also a 1 off type function. Move to separate script??</t>
+  </si>
+  <si>
+    <t>set of unique date strings &amp; tag dict with TPOS</t>
+  </si>
+  <si>
+    <t>set of unique date strings &amp; tag dict w/o TPOS</t>
+  </si>
+  <si>
+    <t>consider making it public??</t>
+  </si>
+  <si>
+    <t>_update_id3</t>
   </si>
 </sst>
 </file>
@@ -379,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -408,6 +609,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1168,16 +1383,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B59A74-3B3D-46A0-BA00-4CC6B3EB725F}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1226,6 +1441,299 @@
       </c>
       <c r="G5" s="4" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+      <c r="F8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="20" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="F13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="F15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="F21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="F23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="F29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="F30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="F32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="F34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="F36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="16"/>
+      <c r="F38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1251,15 +1759,24 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1309,15 +1826,24 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1367,15 +1893,24 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1425,15 +1960,24 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE346F7-4387-4080-B3EA-703CBA3E39CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C7BDE7-2F5A-4346-832B-1515661791C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="151">
   <si>
     <t>package</t>
   </si>
@@ -345,9 +345,6 @@
     <t>map_wma_tags</t>
   </si>
   <si>
-    <t>a pattern valid/invalid in main.py covers this function</t>
-  </si>
-  <si>
     <t>calls load_any_file</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
     <t>this function should be removed, it's just a wrapper for get_media_info_dict. Refactor as needed.</t>
   </si>
   <si>
-    <t>PITA to test, each os returns slightly diff dict, especially filename. Test return dict is not None, has keys/values and 2 inner dicts?</t>
-  </si>
-  <si>
     <t>current media info dict tests is really just a TAGS inner dict test - which is the test for this function</t>
   </si>
   <si>
@@ -457,6 +451,48 @@
   </si>
   <si>
     <t>_update_id3</t>
+  </si>
+  <si>
+    <t>m4a, mp3, wma all with co-located Folder.jpg</t>
+  </si>
+  <si>
+    <t>tests/Music</t>
+  </si>
+  <si>
+    <t>no pattern</t>
+  </si>
+  <si>
+    <t>valid pattern</t>
+  </si>
+  <si>
+    <t>invalid pattern</t>
+  </si>
+  <si>
+    <t>tests/Music *mp3</t>
+  </si>
+  <si>
+    <t>tests/Music/*m3u</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>PITA to test, each os returns slightly diff dict, especially filename. Test return dict is not None, has keys/values and 2 inner dicts? Update linux laptop to v7.1 Run a ffmpeg cli and copy as expected dict.</t>
+  </si>
+  <si>
+    <t>a mp3 with valid metdata</t>
+  </si>
+  <si>
+    <t>one pattern is fine, test is all about acceptting a valid pattern input</t>
+  </si>
+  <si>
+    <t>no pattern (will do all mp3, m4a, wma files)</t>
+  </si>
+  <si>
+    <t>tests/Music .mp3</t>
+  </si>
+  <si>
+    <t>tests/Music .m3u</t>
   </si>
 </sst>
 </file>
@@ -580,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -611,13 +647,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1383,13 +1415,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B59A74-3B3D-46A0-BA00-4CC6B3EB725F}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="118.140625" customWidth="1"/>
@@ -1465,274 +1497,325 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="F8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="18" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" t="s">
         <v>138</v>
       </c>
-      <c r="F7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="F8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="20" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>80</v>
-      </c>
       <c r="G10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="D11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="D12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="F13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="F13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>83</v>
       </c>
       <c r="F14" t="s">
         <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+      <c r="A15" s="2"/>
       <c r="F15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="F17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="F23" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="F25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="F27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="F28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="F31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="F33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="F34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="F36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="F38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="F40" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="F21" t="s">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="F42" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="17"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="F23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="F27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" t="s">
-        <v>115</v>
-      </c>
-      <c r="G28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="F29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="F30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="F32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="F34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="F36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="F38" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
     </row>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C7BDE7-2F5A-4346-832B-1515661791C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B05DE4-C419-47B3-B4AC-02571C92A606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="159">
   <si>
     <t>package</t>
   </si>
@@ -132,9 +132,6 @@
     <t>extract art file with stream &amp; tag</t>
   </si>
   <si>
-    <t>extract artfile w/o stream and with tag</t>
-  </si>
-  <si>
     <t>one test for audio file is accpetable type</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>test_extract_album_art_no_tag_or_stream</t>
   </si>
   <si>
-    <t>test_extract_album_art_with_stream_and_tag</t>
-  </si>
-  <si>
     <t>test_extract_album_art_without_stream_with_tag</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>test_set_album_art</t>
   </si>
   <si>
-    <t>the 3 typed extract functions cover most of this, except for a pattern valid/invalid test in main.py</t>
-  </si>
-  <si>
     <t>test for extract walk valid/invalide pattern</t>
   </si>
   <si>
@@ -360,9 +351,6 @@
     <t>do I even need this any more?? Should I output to file instead of console?</t>
   </si>
   <si>
-    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info. Best to just happy path test converting m4a, mp3, wma and verify output mp3 file has correct text metadata and has art  metadata </t>
-  </si>
-  <si>
     <t>this function should be removed, it's just a wrapper for get_media_info_dict. Refactor as needed.</t>
   </si>
   <si>
@@ -453,9 +441,6 @@
     <t>_update_id3</t>
   </si>
   <si>
-    <t>m4a, mp3, wma all with co-located Folder.jpg</t>
-  </si>
-  <si>
     <t>tests/Music</t>
   </si>
   <si>
@@ -474,25 +459,64 @@
     <t>tests/Music/*m3u</t>
   </si>
   <si>
-    <t>??</t>
-  </si>
-  <si>
     <t>PITA to test, each os returns slightly diff dict, especially filename. Test return dict is not None, has keys/values and 2 inner dicts? Update linux laptop to v7.1 Run a ffmpeg cli and copy as expected dict.</t>
   </si>
   <si>
     <t>a mp3 with valid metdata</t>
   </si>
   <si>
-    <t>one pattern is fine, test is all about acceptting a valid pattern input</t>
-  </si>
-  <si>
-    <t>no pattern (will do all mp3, m4a, wma files)</t>
-  </si>
-  <si>
-    <t>tests/Music .mp3</t>
-  </si>
-  <si>
-    <t>tests/Music .m3u</t>
+    <t>test_extract_album_art</t>
+  </si>
+  <si>
+    <t>extract art file w/o stream and with tag</t>
+  </si>
+  <si>
+    <t>todo</t>
+  </si>
+  <si>
+    <t>pattern valid/invalid tests</t>
+  </si>
+  <si>
+    <t>m4a/mp3/wma w embedded in testSetup built "PreppedMusic"</t>
+  </si>
+  <si>
+    <t>select audio file from SourceMusic for testing and move to a  testSetup built "SourceMusic"?</t>
+  </si>
+  <si>
+    <t>m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic", call with .mp3</t>
+  </si>
+  <si>
+    <t>call with .m3u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info. Best to just happy path test converting m4a, mp3, wma and verify output mp3 file created. Could go as far as checking metdata values and has art tag. </t>
+  </si>
+  <si>
+    <t>no pattern (will do all mp3, m4a, wma files), just confirm mp3 files exist.</t>
+  </si>
+  <si>
+    <t>one pattern is fine, test is all about acceptting a valid pattern input. Confimr mp3 file exists.</t>
+  </si>
+  <si>
+    <t>invalid file type m3u?</t>
+  </si>
+  <si>
+    <t>test_convert_walk</t>
+  </si>
+  <si>
+    <t>test_convert_walk_pattern</t>
+  </si>
+  <si>
+    <t>test_convert_walk_invalid_pattern</t>
+  </si>
+  <si>
+    <t>valid audio files</t>
+  </si>
+  <si>
+    <t>test_convert_file</t>
   </si>
 </sst>
 </file>
@@ -616,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -647,16 +671,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,20 +1019,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -1013,22 +1043,22 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1036,19 +1066,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6" s="5"/>
     </row>
@@ -1057,19 +1087,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>3</v>
@@ -1080,19 +1110,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>5</v>
@@ -1103,19 +1133,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -1124,19 +1154,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" s="3"/>
     </row>
@@ -1145,22 +1175,22 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1168,22 +1198,22 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1191,22 +1221,22 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,10 +1244,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
@@ -1235,10 +1265,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>21</v>
@@ -1256,16 +1286,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>22</v>
@@ -1277,10 +1307,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>21</v>
@@ -1289,7 +1319,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3"/>
     </row>
@@ -1298,10 +1328,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>21</v>
@@ -1319,22 +1349,18 @@
         <v>11</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1342,16 +1368,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>22</v>
@@ -1363,16 +1389,16 @@
         <v>12</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>23</v>
@@ -1384,19 +1410,19 @@
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G22" s="15"/>
     </row>
@@ -1418,49 +1444,49 @@
   <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="118.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -1472,351 +1498,374 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F7" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="F8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="18" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="D11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="G11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="D12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" t="s">
-        <v>144</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>132</v>
+        <v>78</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" t="s">
-        <v>101</v>
+        <v>79</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="F15" t="s">
-        <v>130</v>
+      <c r="F15" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" t="s">
-        <v>102</v>
+        <v>80</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="F17" t="s">
-        <v>128</v>
+      <c r="F17" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" t="s">
-        <v>107</v>
+        <v>81</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>145</v>
+        <v>82</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
+        <v>83</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" t="s">
-        <v>108</v>
+        <v>84</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>101</v>
+        <v>85</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="F23" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="16"/>
+      <c r="F23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="21"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="F25" t="s">
-        <v>125</v>
+      <c r="F25" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F27" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F28" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="F27" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="F28" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G29" t="s">
-        <v>110</v>
+        <v>88</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" t="s">
-        <v>104</v>
+        <v>89</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="F31" t="s">
-        <v>131</v>
+      <c r="F31" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" t="s">
-        <v>111</v>
+        <v>90</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="F33" t="s">
-        <v>114</v>
+      <c r="F33" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="F34" t="s">
-        <v>112</v>
+      <c r="F34" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" t="s">
-        <v>115</v>
+        <v>91</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="F36" t="s">
-        <v>117</v>
+      <c r="F36" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" t="s">
-        <v>123</v>
+        <v>92</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="F38" t="s">
-        <v>122</v>
+      <c r="F38" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" t="s">
-        <v>121</v>
+        <v>93</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="F40" t="s">
-        <v>120</v>
+      <c r="F40" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F41" t="s">
-        <v>118</v>
+        <v>94</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="F42" t="s">
-        <v>119</v>
+      <c r="F42" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1843,20 +1892,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -1868,10 +1917,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -1883,7 +1932,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1910,20 +1959,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -1935,10 +1984,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -1950,7 +1999,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1977,20 +2026,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2002,10 +2051,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -2017,7 +2066,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2044,20 +2093,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2069,10 +2118,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -2084,7 +2133,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2113,12 +2162,12 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2127,10 +2176,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
@@ -2142,32 +2191,32 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B05DE4-C419-47B3-B4AC-02571C92A606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19591A5E-AB2B-464C-8F10-CBDB10273D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
+    <workbookView xWindow="-8220" yWindow="-13056" windowWidth="23232" windowHeight="12552" xr2:uid="{94B5C224-BB4D-4292-8301-349538C48A0E}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="167">
   <si>
     <t>package</t>
   </si>
@@ -517,13 +517,37 @@
   </si>
   <si>
     <t>test_convert_file</t>
+  </si>
+  <si>
+    <t>test_extract_walk_invalid_pattern</t>
+  </si>
+  <si>
+    <t>extract walk with invalid pattern</t>
+  </si>
+  <si>
+    <t>test_extract_walk_pattern</t>
+  </si>
+  <si>
+    <t>test_extract_walk</t>
+  </si>
+  <si>
+    <t>extract walk without a pattern</t>
+  </si>
+  <si>
+    <t>extract walk with a pattern</t>
+  </si>
+  <si>
+    <t>.m3u with testSetup built "PreppedMusic"</t>
+  </si>
+  <si>
+    <t>.mp3 w embedded in testSetup built "PreppedMusic"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,11 +560,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -640,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -649,9 +668,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1001,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240D0244-C07C-4B0D-B34B-DEFFB8A00779}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1062,7 +1078,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1083,7 +1099,7 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1106,7 +1122,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1129,7 +1145,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1138,7 +1154,7 @@
       <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1150,7 +1166,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1159,7 +1175,7 @@
       <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1171,7 +1187,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1194,7 +1210,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1217,7 +1233,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1240,7 +1256,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1261,7 +1277,7 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1282,7 +1298,7 @@
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1303,7 +1319,7 @@
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1324,7 +1340,7 @@
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1345,7 +1361,7 @@
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1354,86 +1370,132 @@
       <c r="C19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="14" t="s">
+      <c r="D19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="13" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="14" t="s">
+      <c r="B24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G24">
-    <sortCondition ref="A6:A42"/>
-    <sortCondition ref="E6:E42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G26">
+    <sortCondition ref="A6:A44"/>
+    <sortCondition ref="E6:E44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1502,7 +1564,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1554,53 +1616,53 @@
       <c r="E9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:7" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="B10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="16" t="s">
+    <row r="11" spans="1:7" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="15" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1625,10 +1687,10 @@
       <c r="A13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1679,7 +1741,7 @@
       <c r="F19" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1706,7 +1768,7 @@
       <c r="F22" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="20" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1714,7 +1776,7 @@
       <c r="F23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F546789D-9915-4E5F-92A9-989B808C7E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="AudioArt"/>
-    <sheet r:id="rId2" sheetId="2" name="AudioMetadata"/>
-    <sheet r:id="rId3" sheetId="3" name="AudioPlaylist"/>
-    <sheet r:id="rId4" sheetId="4" name="AudioNormalization"/>
-    <sheet r:id="rId5" sheetId="5" name="DirectoryProcessing"/>
-    <sheet r:id="rId6" sheetId="6" name="SubprocessUtilities"/>
-    <sheet r:id="rId7" sheetId="7" name="Main"/>
+    <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
+    <sheet name="AudioMetadata" sheetId="2" r:id="rId2"/>
+    <sheet name="AudioPlaylist" sheetId="3" r:id="rId3"/>
+    <sheet name="AudioNormalization" sheetId="4" r:id="rId4"/>
+    <sheet name="DirectoryProcessing" sheetId="5" r:id="rId5"/>
+    <sheet name="SubprocessUtilities" sheetId="6" r:id="rId6"/>
+    <sheet name="Main" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="169">
   <si>
     <t>package</t>
   </si>
@@ -136,27 +142,18 @@
     <t>convert_walk</t>
   </si>
   <si>
-    <t>no pattern</t>
-  </si>
-  <si>
     <t>test_convert_walk</t>
   </si>
   <si>
     <t>no pattern (will do all mp3, m4a, wma files), just confirm mp3 files exist.</t>
   </si>
   <si>
-    <t>valid pattern</t>
-  </si>
-  <si>
     <t>test_convert_walk_pattern</t>
   </si>
   <si>
     <t>m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic", call with .mp3</t>
   </si>
   <si>
-    <t>one pattern is fine, test is all about acceptting a valid pattern input. Confimr mp3 file exists.</t>
-  </si>
-  <si>
     <t>invalid pattern</t>
   </si>
   <si>
@@ -518,13 +515,30 @@
   </si>
   <si>
     <t>in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
+  </si>
+  <si>
+    <t>test_convert_file_no_jpg</t>
+  </si>
+  <si>
+    <t>happy path - valid audio files w/Folder.jpgs</t>
+  </si>
+  <si>
+    <t>happy path - no pattern</t>
+  </si>
+  <si>
+    <t>happy path - valid pattern</t>
+  </si>
+  <si>
+    <t>mp3 w/o co-located Folder.jpg</t>
+  </si>
+  <si>
+    <t>one pattern is fine, test is all about acceptting a valid pattern input. Call with mp3 patter, confirm that converted mp3 file exists.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -549,21 +563,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFbfbfbf"/>
+        <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdae3f3"/>
+        <fgColor rgb="FFDAE3F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe2f0d9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -598,7 +612,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -613,13 +627,13 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,13 +642,13 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,67 +657,105 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -714,10 +766,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -755,71 +807,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -847,7 +899,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -870,11 +922,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -883,13 +935,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -899,7 +951,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -908,7 +960,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -917,7 +969,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -925,10 +977,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -993,521 +1045,485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="19.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="63.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="46.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="48.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="45.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
-      <c r="A7" s="9" t="s">
+      <c r="G8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="6" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="10" t="s">
+      <c r="F9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
-      <c r="A11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
-      <c r="A12" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="6" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
-      <c r="A13" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
-      <c r="A14" s="5" t="s">
+      <c r="F14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="6" t="s">
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
-      <c r="A15" s="10" t="s">
+      <c r="F15" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
-      <c r="A16" s="12" t="s">
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
-      <c r="A17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
-      <c r="A18" s="9" t="s">
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
-      <c r="A19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="E20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="F20" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
-      <c r="A20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F21" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
-      <c r="A21" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="E22" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
-      <c r="A22" s="10" t="s">
+      <c r="F22" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
-      <c r="A23" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="B24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G24" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1515,642 +1531,640 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="15.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="32.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="47.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="118.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    </row>
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="1" t="s">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="45">
-      <c r="A9" s="1" t="s">
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="E10" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="32.25">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="G11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="45">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="F12" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="G12" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="E13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="F13" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G14" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="33">
-      <c r="A13" s="1" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="8" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G15" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1" t="s">
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1" t="s">
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="1" t="s">
+      <c r="G17" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1" t="s">
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1" t="s">
+    <row r="20" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="1" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1" t="s">
+      <c r="G20" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="32.25">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="1" t="s">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="7" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="1" t="s">
+      <c r="G23" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="12" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="1" t="s">
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="1" t="s">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="1" t="s">
+      <c r="G25" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="1" t="s">
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="1" t="s">
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="12" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="1" t="s">
+      <c r="G27" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="1" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="1" t="s">
+      <c r="G28" s="13"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G29" s="13"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="1" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="1" t="s">
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
-      <c r="A29" s="1" t="s">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1" t="s">
+      <c r="G31" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="1" t="s">
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="1" t="s">
+      <c r="G33" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
-      <c r="A32" s="1" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="1" t="s">
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="1" t="s">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="1" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
-      <c r="A35" s="1" t="s">
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="1" t="s">
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
-      <c r="A37" s="1" t="s">
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="1" t="s">
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="1" t="s">
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18">
-      <c r="A39" s="1" t="s">
+      <c r="G41" s="13"/>
+    </row>
+    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="1" t="s">
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="1" t="s">
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18">
-      <c r="A41" s="1" t="s">
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="1" t="s">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="1" t="s">
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18">
-      <c r="A43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18">
-      <c r="A44" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18">
-      <c r="A45" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2158,90 +2172,67 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2251,90 +2242,67 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2344,90 +2312,67 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2437,90 +2382,67 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2530,141 +2452,85 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="8.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="38.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F546789D-9915-4E5F-92A9-989B808C7E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAE3568-79AD-41C8-B973-E3276CF16D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="173">
   <si>
     <t>package</t>
   </si>
@@ -157,9 +157,6 @@
     <t>invalid pattern</t>
   </si>
   <si>
-    <t>test_convert_walk_invalid_pattern</t>
-  </si>
-  <si>
     <t>call with .m3u</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>select audio file from SourceMusic for testing and move to a  testSetup built "SourceMusic"?</t>
   </si>
   <si>
-    <t>calls get_media_tags, make_album_dir, move_audio_file, create_csv. WILL modify /test/Music, which I do not want. Is also a 1 off type function. Move to separate script??</t>
-  </si>
-  <si>
     <t>get_any_tags</t>
   </si>
   <si>
@@ -533,6 +527,24 @@
   </si>
   <si>
     <t>one pattern is fine, test is all about acceptting a valid pattern input. Call with mp3 patter, confirm that converted mp3 file exists.</t>
+  </si>
+  <si>
+    <t>test_convert_walk_pattern_invalid</t>
+  </si>
+  <si>
+    <t>test_get_any_tags</t>
+  </si>
+  <si>
+    <t>test_get_any_tags_wo_metadata</t>
+  </si>
+  <si>
+    <t>test_create_album_dir</t>
+  </si>
+  <si>
+    <t>calls get_media_tags, make_album_dir, move_audio_file, create_csv. WILL modify /test/Music, which I do not want. Is also a one off type function. Needs a direcotry created by setUp. Only do happyu path,</t>
+  </si>
+  <si>
+    <t>calls load_any_file. Happy path with all 3 audio file types.</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1100,10 +1112,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
@@ -1132,7 +1144,7 @@
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>25</v>
@@ -1150,12 +1162,12 @@
         <v>26</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>25</v>
@@ -1173,33 +1185,33 @@
         <v>26</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>32</v>
@@ -1208,19 +1220,19 @@
         <v>32</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>32</v>
@@ -1229,21 +1241,21 @@
         <v>32</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>32</v>
@@ -1252,21 +1264,21 @@
         <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>32</v>
@@ -1275,63 +1287,63 @@
         <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>32</v>
@@ -1340,40 +1352,40 @@
         <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>32</v>
@@ -1382,42 +1394,42 @@
         <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>32</v>
@@ -1426,19 +1438,19 @@
         <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>32</v>
@@ -1447,40 +1459,40 @@
         <v>32</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="F22" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>32</v>
@@ -1489,34 +1501,34 @@
         <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="G24" s="5"/>
     </row>
@@ -1653,7 +1665,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>34</v>
@@ -1679,10 +1691,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G10" s="11"/>
     </row>
@@ -1697,7 +1709,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>38</v>
@@ -1710,7 +1722,9 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
@@ -1718,7 +1732,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>40</v>
@@ -1727,11 +1741,13 @@
         <v>41</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="B13" s="12" t="s">
         <v>32</v>
       </c>
@@ -1742,67 +1758,87 @@
         <v>42</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="G14" s="15" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+        <v>46</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="E15" s="13" t="s">
+        <v>168</v>
+      </c>
       <c r="F15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1812,13 +1848,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -1826,27 +1862,27 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -1854,12 +1890,12 @@
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1867,22 +1903,22 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1892,23 +1928,23 @@
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1918,23 +1954,23 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1944,7 +1980,7 @@
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G28" s="13"/>
     </row>
@@ -1955,13 +1991,13 @@
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1969,22 +2005,22 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1994,23 +2030,23 @@
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G32" s="13"/>
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2020,7 +2056,7 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G34" s="11"/>
     </row>
@@ -2031,23 +2067,23 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
       <c r="F36" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2057,20 +2093,20 @@
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="F37" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G38" s="11"/>
     </row>
@@ -2081,20 +2117,20 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G40" s="13"/>
     </row>
@@ -2105,20 +2141,20 @@
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
       <c r="F41" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G42" s="11"/>
     </row>
@@ -2129,13 +2165,13 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -2146,7 +2182,7 @@
     </row>
     <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2157,7 +2193,7 @@
     </row>
     <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C27F3-D7AB-4EDB-B8BE-BF6D56E5AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="-8220" yWindow="-13056" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="AudioArt"/>
-    <sheet r:id="rId2" sheetId="2" name="AudioMetadata"/>
-    <sheet r:id="rId3" sheetId="3" name="AudioPlaylist"/>
-    <sheet r:id="rId4" sheetId="4" name="AudioNormalization"/>
-    <sheet r:id="rId5" sheetId="5" name="DirectoryProcessing"/>
-    <sheet r:id="rId6" sheetId="6" name="SubprocessUtilities"/>
-    <sheet r:id="rId7" sheetId="7" name="Main"/>
+    <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
+    <sheet name="AudioMetadata" sheetId="2" r:id="rId2"/>
+    <sheet name="AudioPlaylist" sheetId="3" r:id="rId3"/>
+    <sheet name="AudioNormalization" sheetId="4" r:id="rId4"/>
+    <sheet name="DirectoryProcessing" sheetId="5" r:id="rId5"/>
+    <sheet name="SubprocessUtilities" sheetId="6" r:id="rId6"/>
+    <sheet name="Main" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="175">
   <si>
     <t>package</t>
   </si>
@@ -550,8 +556,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -573,7 +578,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,21 +587,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFbfbfbf"/>
+        <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdae3f3"/>
+        <fgColor rgb="FFDAE3F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe2f0d9"/>
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -637,7 +648,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,7 +657,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -661,13 +672,13 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,13 +687,13 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -691,85 +702,143 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -780,10 +849,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -821,71 +890,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -913,7 +982,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -936,11 +1005,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -949,13 +1018,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -965,7 +1034,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -974,7 +1043,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -983,7 +1052,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -991,10 +1060,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1059,521 +1128,485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="19.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="63.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="46.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="48.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="45.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="15" t="s">
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="17" t="s">
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="17" t="s">
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="16" t="s">
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="B15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G15" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="18" t="s">
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="B16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G16" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="14" t="s">
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="B17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G17" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="15" t="s">
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="32.25">
-      <c r="A19" s="14" t="s">
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="B19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="9" t="s">
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="14" t="s">
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="B21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="16" t="s">
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="B22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G22" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="18" t="s">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="B23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="45.75">
-      <c r="A24" s="14" t="s">
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="B24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="G24" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1581,737 +1614,768 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="32.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="47.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="118.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    </row>
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="7" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="9" t="s">
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="9" t="s">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="45">
-      <c r="A9" s="8" t="s">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="45">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="32.25">
-      <c r="A11" s="9" t="s">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="45">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="B12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="33">
-      <c r="A14" s="8" t="s">
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="8" t="s">
+      <c r="G16" s="21"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="E17" s="22"/>
+      <c r="F17" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="10" t="s">
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="32.25">
-      <c r="A19" s="8" t="s">
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8" t="s">
+      <c r="B19" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8" t="s">
+      <c r="E19" s="24"/>
+      <c r="F19" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8" t="s">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="9" t="s">
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="35.25">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
-      <c r="A22" s="9" t="s">
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="8" t="s">
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+    </row>
+    <row r="23" spans="1:7" s="18" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8" t="s">
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="5"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="10" t="s">
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="9" t="s">
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="13" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="21"/>
+      <c r="F25" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9" t="s">
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="8" t="s">
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8" t="s">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8" t="s">
+      <c r="E27" s="22"/>
+      <c r="F27" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="10" t="s">
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8" t="s">
+      <c r="E28" s="22"/>
+      <c r="F28" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="9" t="s">
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="9" t="s">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="9" t="s">
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="9" t="s">
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G31" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
-      <c r="A32" s="8" t="s">
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="11" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="8" t="s">
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="9" t="s">
+      <c r="E33" s="21"/>
+      <c r="F33" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10" t="s">
+    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="9" t="s">
+      <c r="E34" s="21"/>
+      <c r="F34" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G34" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
-      <c r="A35" s="8" t="s">
+      <c r="G34" s="21"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8" t="s">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="22" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8" t="s">
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8" t="s">
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G37" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18">
-      <c r="A38" s="9" t="s">
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="9" t="s">
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="16" t="s">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9" t="s">
+    <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18">
-      <c r="A40" s="8" t="s">
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="s">
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8" t="s">
+      <c r="G40" s="22"/>
+    </row>
+    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18">
-      <c r="A42" s="9" t="s">
+      <c r="G41" s="22"/>
+    </row>
+    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="9" t="s">
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="9" t="s">
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18">
-      <c r="A44" s="8" t="s">
+      <c r="G43" s="21"/>
+    </row>
+    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8" t="s">
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="G44" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8" t="s">
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="G45" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18">
-      <c r="A46" s="9" t="s">
+      <c r="G45" s="22"/>
+    </row>
+    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18">
-      <c r="A47" s="8" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18">
-      <c r="A48" s="9" t="s">
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+    </row>
+    <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2319,90 +2383,67 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2412,90 +2453,67 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2505,90 +2523,67 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2598,90 +2593,67 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2691,141 +2663,85 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="8.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="38.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="4.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="6.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C27F3-D7AB-4EDB-B8BE-BF6D56E5AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3E51FF-A7FA-484A-81FB-0292DB2321DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8220" yWindow="-13056" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="178">
   <si>
     <t>package</t>
   </si>
@@ -551,6 +551,15 @@
   </si>
   <si>
     <t>in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
+  </si>
+  <si>
+    <t>check if metadata_type = audio_file.__class__.__name__ is MP4</t>
+  </si>
+  <si>
+    <t>check if metadata_type = audio_file.__class__.__name__ is ASF</t>
+  </si>
+  <si>
+    <t>check if audio_file.__class__.__name__ is MP4/MP3/ASF</t>
   </si>
 </sst>
 </file>
@@ -744,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -795,7 +804,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -811,12 +819,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -826,6 +828,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1781,13 +1786,13 @@
       <c r="C11" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="15" t="s">
@@ -1804,13 +1809,13 @@
       <c r="C12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G12" s="16" t="s">
@@ -1836,28 +1841,28 @@
       <c r="F13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="22" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1865,16 +1870,16 @@
       <c r="A15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="21" t="s">
+      <c r="B15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>57</v>
       </c>
       <c r="F15" s="16" t="s">
@@ -1888,92 +1893,92 @@
       <c r="A16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="21" t="s">
+      <c r="B16" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="20" t="s">
         <v>61</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22" t="s">
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="24" t="s">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24" t="s">
+      <c r="E19" s="16"/>
+      <c r="F19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22" t="s">
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2007,50 +2012,50 @@
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
     </row>
-    <row r="23" spans="1:7" s="18" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27" t="s">
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="21"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="16" t="s">
         <v>77</v>
       </c>
@@ -2062,67 +2067,67 @@
       <c r="A26" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21" t="s">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="16" t="s">
         <v>79</v>
       </c>
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22" t="s">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22" t="s">
+      <c r="E27" s="21"/>
+      <c r="F27" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22" t="s">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="22"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2130,38 +2135,38 @@
       <c r="A30" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="21"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
       <c r="F31" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G31" s="21"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="23" t="s">
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="22" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2169,12 +2174,12 @@
       <c r="A33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="24" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="21"/>
+      <c r="E33" s="20"/>
       <c r="F33" s="16" t="s">
         <v>92</v>
       </c>
@@ -2186,66 +2191,68 @@
       <c r="A34" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21" t="s">
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="21"/>
+      <c r="E34" s="20"/>
       <c r="F34" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G34" s="21"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22" t="s">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22" t="s">
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="22"/>
+      <c r="G36" s="21"/>
     </row>
     <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22" t="s">
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="G37" s="22"/>
-    </row>
-    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="21"/>
+    </row>
+    <row r="38" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="27" t="s">
+        <v>177</v>
+      </c>
       <c r="F38" s="16" t="s">
         <v>77</v>
       </c>
@@ -2257,125 +2264,131 @@
       <c r="A39" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
       <c r="F39" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="21"/>
-    </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
+      <c r="G39" s="20"/>
+    </row>
+    <row r="40" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22" t="s">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="22"/>
+      <c r="G40" s="21"/>
     </row>
     <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22" t="s">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="22"/>
-    </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G41" s="21"/>
+    </row>
+    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="27" t="s">
+        <v>175</v>
+      </c>
       <c r="F42" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="21"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="21"/>
-    </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
+      <c r="G43" s="20"/>
+    </row>
+    <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22" t="s">
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="F44" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="G44" s="22"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="G45" s="22"/>
+      <c r="G45" s="21"/>
     </row>
     <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3E51FF-A7FA-484A-81FB-0292DB2321DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B3389C-A2C3-4493-B7CB-F73DFC2F2918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,12 +21,23 @@
     <sheet name="SubprocessUtilities" sheetId="6" r:id="rId6"/>
     <sheet name="Main" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="178">
   <si>
     <t>package</t>
   </si>
@@ -112,15 +123,6 @@
     <t>_update_id3</t>
   </si>
   <si>
-    <t>set of unique date strings &amp; tag dict with TPOS</t>
-  </si>
-  <si>
-    <t>consider making it public??</t>
-  </si>
-  <si>
-    <t>set of unique date strings &amp; tag dict w/o TPOS</t>
-  </si>
-  <si>
     <t>convert_file</t>
   </si>
   <si>
@@ -560,6 +562,15 @@
   </si>
   <si>
     <t>check if audio_file.__class__.__name__ is MP4/MP3/ASF</t>
+  </si>
+  <si>
+    <t>set of unique date strings &amp; tag dict w/o TPOS and with TYER = 1900</t>
+  </si>
+  <si>
+    <t>test_update_id3</t>
+  </si>
+  <si>
+    <t>update tags with max unique date and setting tpos value if necessary</t>
   </si>
 </sst>
 </file>
@@ -829,7 +840,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1162,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,10 +1199,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
@@ -1220,7 +1231,7 @@
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -1238,12 +1249,12 @@
         <v>26</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
@@ -1261,350 +1272,350 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="G19" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>169</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -1623,7 +1634,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -1704,691 +1715,684 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6" t="s">
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="G10" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="B11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="15" t="s">
+      <c r="F11" s="19" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>44</v>
+        <v>29</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="F12" s="16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="16" t="s">
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="B13" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="E13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="F13" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="G13" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="21" t="s">
+      <c r="D14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>55</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="16" t="s">
         <v>59</v>
       </c>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="A16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="G16" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="B18" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21" t="s">
+      <c r="G18" s="19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="D20" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>70</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
     </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-    </row>
-    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24" t="s">
+      <c r="E24" s="20"/>
+      <c r="F24" s="16" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
+      <c r="G24" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="23" t="s">
-        <v>76</v>
-      </c>
+      <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="16" t="s">
+      <c r="G26" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>52</v>
+      <c r="D27" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="16" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21" t="s">
+      <c r="G28" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B29" s="20"/>
-      <c r="C29" s="20" t="s">
-        <v>25</v>
-      </c>
+      <c r="C29" s="20"/>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
       <c r="F29" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>86</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
       <c r="F30" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="16" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
-      <c r="D33" s="16" t="s">
-        <v>52</v>
+      <c r="D33" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="E33" s="20"/>
       <c r="F33" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="16" t="s">
+      <c r="G34" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>97</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="G35" s="21"/>
     </row>
     <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="21"/>
-    </row>
-    <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="G37" s="21"/>
-    </row>
-    <row r="38" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
-      <c r="E38" s="27" t="s">
-        <v>177</v>
-      </c>
+      <c r="E38" s="20"/>
       <c r="F38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="21" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>100</v>
-      </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G39" s="20"/>
-    </row>
-    <row r="40" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>103</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
-      <c r="E40" s="22" t="s">
-        <v>175</v>
-      </c>
+      <c r="E40" s="21"/>
       <c r="F40" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="21"/>
+    </row>
+    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="21"/>
-    </row>
-    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="G41" s="20"/>
+    </row>
+    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>103</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="21"/>
-    </row>
-    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>106</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="27" t="s">
-        <v>175</v>
-      </c>
+      <c r="E42" s="20"/>
       <c r="F42" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" s="20"/>
+    </row>
+    <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="20"/>
-    </row>
-    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="G43" s="21"/>
+    </row>
+    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>106</v>
-      </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="G43" s="20"/>
-    </row>
-    <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>109</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="22" t="s">
-        <v>176</v>
-      </c>
+      <c r="E44" s="21"/>
       <c r="F44" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G44" s="21"/>
+    </row>
+    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+    </row>
+    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="G44" s="21"/>
-    </row>
-    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G45" s="21"/>
-    </row>
-    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-    </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-    </row>
-    <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B3389C-A2C3-4493-B7CB-F73DFC2F2918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D29FF3F-6262-4BB9-8D15-4114A1621158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="192">
   <si>
     <t>package</t>
   </si>
@@ -138,12 +138,6 @@
     <t>m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic"</t>
   </si>
   <si>
-    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info. Best to just happy path test converting m4a, mp3, wma and verify output mp3 file created. Could go as far as checking metdata values and has art tag. </t>
-  </si>
-  <si>
-    <t>valid audio files</t>
-  </si>
-  <si>
     <t>test_convert_file_no_jpg</t>
   </si>
   <si>
@@ -571,6 +565,54 @@
   </si>
   <si>
     <t>update tags with max unique date and setting tpos value if necessary</t>
+  </si>
+  <si>
+    <t>valid audio files w/o co-located folder.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info. Best to just happy path test converting m4a, mp3, wma and verify output mp3 file created. Test support fuinctions seperately.. </t>
+  </si>
+  <si>
+    <t>path_info</t>
+  </si>
+  <si>
+    <t>get path for non-audio file</t>
+  </si>
+  <si>
+    <t>get path for audio file</t>
+  </si>
+  <si>
+    <t>test_path_info_not_audio</t>
+  </si>
+  <si>
+    <t>expected.m3u</t>
+  </si>
+  <si>
+    <t>joshua davis m4a</t>
+  </si>
+  <si>
+    <t>test_get_file_directory_none</t>
+  </si>
+  <si>
+    <t>fail path not find directroy path of file</t>
+  </si>
+  <si>
+    <t>happy path find directory path of file</t>
+  </si>
+  <si>
+    <t>test_get_file_directory</t>
+  </si>
+  <si>
+    <t>get_file_directory</t>
+  </si>
+  <si>
+    <t>audio file &lt;tld&gt;/&lt;artist&gt;/&lt;album&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
+  </si>
+  <si>
+    <t>audio file &lt;tld&gt;/&lt;artist&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
+  </si>
+  <si>
+    <t>test_path_info</t>
   </si>
 </sst>
 </file>
@@ -764,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -842,6 +884,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1173,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1199,10 +1250,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
@@ -1231,7 +1282,7 @@
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -1249,12 +1300,12 @@
         <v>26</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
@@ -1272,33 +1323,33 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>29</v>
@@ -1307,19 +1358,19 @@
         <v>29</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>29</v>
@@ -1328,21 +1379,21 @@
         <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
@@ -1351,21 +1402,21 @@
         <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
@@ -1374,63 +1425,63 @@
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="F14" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>29</v>
@@ -1439,40 +1490,40 @@
         <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>29</v>
@@ -1481,42 +1532,42 @@
         <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="F19" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="G19" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>29</v>
@@ -1525,19 +1576,19 @@
         <v>29</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>29</v>
@@ -1546,40 +1597,40 @@
         <v>29</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>29</v>
@@ -1588,34 +1639,34 @@
         <v>29</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -1646,7 +1697,7 @@
     <col min="7" max="7" width="118.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1654,7 +1705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1662,7 +1713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1670,8 +1721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
@@ -1726,17 +1776,17 @@
         <v>29</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -1756,10 +1806,10 @@
         <v>32</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
@@ -1769,87 +1819,87 @@
       <c r="C9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="B10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="19" t="s">
+      <c r="F11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="G11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="19" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="E12" s="16" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="16" t="s">
+      <c r="F12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>46</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>48</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>29</v>
@@ -1858,101 +1908,101 @@
         <v>25</v>
       </c>
       <c r="D13" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="G13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="21" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="B14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="20" t="s">
+      <c r="G14" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="16" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="E15" s="20" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="20" t="s">
+      <c r="F15" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>60</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="21"/>
     </row>
-    <row r="18" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>29</v>
@@ -1961,115 +2011,115 @@
         <v>29</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>65</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>67</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
     </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
     </row>
-    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
@@ -2078,49 +2128,49 @@
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G25" s="16"/>
     </row>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G27" s="21"/>
     </row>
-    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20" t="s">
@@ -2129,41 +2179,41 @@
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
       <c r="F28" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
       <c r="F29" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
       <c r="F30" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G30" s="20"/>
     </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2171,199 +2221,199 @@
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
       <c r="G31" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E32" s="20"/>
       <c r="F32" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
       <c r="D33" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E33" s="20"/>
       <c r="F33" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G33" s="20"/>
     </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G35" s="21"/>
     </row>
-    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G36" s="21"/>
     </row>
     <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
       <c r="D37" s="20"/>
       <c r="E37" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
       <c r="F38" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
       <c r="E39" s="22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G39" s="21"/>
     </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G40" s="21"/>
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
       <c r="E43" s="22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G43" s="21"/>
     </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -2372,9 +2422,9 @@
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
     </row>
-    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -2383,9 +2433,9 @@
       <c r="F46" s="21"/>
       <c r="G46" s="21"/>
     </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -2544,15 +2594,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="46.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2582,27 +2632,111 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="28" t="s">
         <v>2</v>
       </c>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="30"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="G9" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D29FF3F-6262-4BB9-8D15-4114A1621158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B40DED-4958-45F4-AD95-AB2AB7314BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -889,9 +889,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2655,46 +2652,46 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="30" t="s">
+      <c r="B6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="30" t="s">
+      <c r="B7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="G7" s="30"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B40DED-4958-45F4-AD95-AB2AB7314BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB950966-36FE-4082-94AB-A4E846073EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="172">
   <si>
     <t>package</t>
   </si>
@@ -210,21 +210,6 @@
     <t>test_get_any_tags_wo_metadata</t>
   </si>
   <si>
-    <t>valid audio w/o metadata: m4a, mp3, wma</t>
-  </si>
-  <si>
-    <t>get_m4a_tags</t>
-  </si>
-  <si>
-    <t>m4a with metadata</t>
-  </si>
-  <si>
-    <t>call load_m4a_file</t>
-  </si>
-  <si>
-    <t>m4a w/o metadata</t>
-  </si>
-  <si>
     <t>get_media_info</t>
   </si>
   <si>
@@ -264,18 +249,6 @@
     <t>invalid file type m3u?</t>
   </si>
   <si>
-    <t>get_mp3_tags</t>
-  </si>
-  <si>
-    <t>mp3 with metadata</t>
-  </si>
-  <si>
-    <t>calls load_mp3_file</t>
-  </si>
-  <si>
-    <t>mp3 w/o metadata</t>
-  </si>
-  <si>
     <t>get_tags_walk</t>
   </si>
   <si>
@@ -297,18 +270,6 @@
     <t>calls get_media_tags. Very much a 1 off, maybe move to separate script? Could laso be converted to file output.</t>
   </si>
   <si>
-    <t>get_wma_tags</t>
-  </si>
-  <si>
-    <t>wma with metadata</t>
-  </si>
-  <si>
-    <t>calls load_wma_file</t>
-  </si>
-  <si>
-    <t>wma w/o metadata</t>
-  </si>
-  <si>
     <t>has_art_tag</t>
   </si>
   <si>
@@ -333,33 +294,6 @@
     <t>invalid file type</t>
   </si>
   <si>
-    <t>load_m4a_file</t>
-  </si>
-  <si>
-    <t>m4a</t>
-  </si>
-  <si>
-    <t>not m4a</t>
-  </si>
-  <si>
-    <t>load_mp3_file</t>
-  </si>
-  <si>
-    <t>mp3</t>
-  </si>
-  <si>
-    <t>not mp3</t>
-  </si>
-  <si>
-    <t>load_wma_file</t>
-  </si>
-  <si>
-    <t>wma</t>
-  </si>
-  <si>
-    <t>not wma</t>
-  </si>
-  <si>
     <t>map_m4a_tags</t>
   </si>
   <si>
@@ -549,12 +483,6 @@
     <t>in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
   </si>
   <si>
-    <t>check if metadata_type = audio_file.__class__.__name__ is MP4</t>
-  </si>
-  <si>
-    <t>check if metadata_type = audio_file.__class__.__name__ is ASF</t>
-  </si>
-  <si>
     <t>check if audio_file.__class__.__name__ is MP4/MP3/ASF</t>
   </si>
   <si>
@@ -613,6 +541,18 @@
   </si>
   <si>
     <t>test_path_info</t>
+  </si>
+  <si>
+    <t>test_get_any_tags_invalid_file</t>
+  </si>
+  <si>
+    <t>non-audio file</t>
+  </si>
+  <si>
+    <t>valid audio w/o metadata</t>
+  </si>
+  <si>
+    <t>only need to test with one audio file type</t>
   </si>
 </sst>
 </file>
@@ -806,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -891,6 +831,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1221,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1247,10 +1197,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
@@ -1279,7 +1229,7 @@
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -1297,12 +1247,12 @@
         <v>26</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
@@ -1320,12 +1270,12 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>29</v>
@@ -1334,19 +1284,19 @@
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>29</v>
@@ -1355,19 +1305,19 @@
         <v>29</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>29</v>
@@ -1376,21 +1326,21 @@
         <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
@@ -1399,21 +1349,21 @@
         <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
@@ -1422,21 +1372,21 @@
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
@@ -1445,19 +1395,19 @@
         <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>29</v>
@@ -1466,19 +1416,19 @@
         <v>29</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>29</v>
@@ -1487,19 +1437,19 @@
         <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>29</v>
@@ -1508,19 +1458,19 @@
         <v>29</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>29</v>
@@ -1529,19 +1479,19 @@
         <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>29</v>
@@ -1550,21 +1500,21 @@
         <v>29</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>29</v>
@@ -1573,19 +1523,19 @@
         <v>29</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>29</v>
@@ -1594,19 +1544,19 @@
         <v>29</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>29</v>
@@ -1615,19 +1565,19 @@
         <v>29</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>29</v>
@@ -1636,19 +1586,19 @@
         <v>29</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>29</v>
@@ -1657,13 +1607,13 @@
         <v>29</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -1682,7 +1632,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -1773,13 +1723,13 @@
         <v>29</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="G7" s="6"/>
     </row>
@@ -1803,7 +1753,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1817,7 +1767,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>33</v>
@@ -1954,492 +1904,327 @@
         <v>55</v>
       </c>
       <c r="E15" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F16" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="21" t="s">
+      <c r="B17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>47</v>
-      </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21" t="s">
-        <v>67</v>
-      </c>
+      <c r="A19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17" t="s">
+      <c r="A21" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="D21" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="20"/>
+      <c r="F23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="23" t="s">
-        <v>71</v>
-      </c>
+      <c r="D24" s="20"/>
       <c r="E24" s="20"/>
       <c r="F24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="16" t="s">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="24" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="16" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="16"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="G27" s="26"/>
+    </row>
+    <row r="28" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21" t="s">
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="21" t="s">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21" t="s">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="G29" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="16" t="s">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="G28" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F31" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
-      <c r="D32" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19" t="s">
+        <v>148</v>
+      </c>
       <c r="F32" s="16" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
-      <c r="D33" s="20" t="s">
-        <v>55</v>
-      </c>
+      <c r="D33" s="20"/>
       <c r="E33" s="20"/>
       <c r="F33" s="16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="G35" s="21"/>
+      <c r="A34" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="21"/>
-    </row>
-    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="G38" s="20"/>
-    </row>
-    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="G39" s="21"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G40" s="21"/>
-    </row>
-    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G41" s="20"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" s="20"/>
-    </row>
-    <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="G43" s="21"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G44" s="21"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
+      <c r="A36" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2653,7 +2438,7 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>29</v>
@@ -2662,19 +2447,19 @@
         <v>29</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>29</v>
@@ -2683,19 +2468,19 @@
         <v>29</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>29</v>
@@ -2704,19 +2489,19 @@
         <v>29</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>29</v>
@@ -2725,13 +2510,13 @@
         <v>29</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="G9" s="29"/>
     </row>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB950966-36FE-4082-94AB-A4E846073EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C213FA2-8652-4789-9C67-E74CB2AF883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="177">
   <si>
     <t>package</t>
   </si>
@@ -231,9 +231,6 @@
     <t>get_media_tags</t>
   </si>
   <si>
-    <t>current media info dict tests is really just a TAGS inner dict test - which is the test for this function</t>
-  </si>
-  <si>
     <t>get_metadata_type</t>
   </si>
   <si>
@@ -252,18 +249,9 @@
     <t>get_tags_walk</t>
   </si>
   <si>
-    <t>tests/Music</t>
-  </si>
-  <si>
     <t>calls get_media_tags OR get_metadata_type, then appropriate get_m4a/mp3/wma_tags. Also a pattern valid/invalid type.</t>
   </si>
   <si>
-    <t>tests/Music *mp3</t>
-  </si>
-  <si>
-    <t>tests/Music/*m3u</t>
-  </si>
-  <si>
     <t>get_uniquie_media_keys</t>
   </si>
   <si>
@@ -553,6 +541,33 @@
   </si>
   <si>
     <t>only need to test with one audio file type</t>
+  </si>
+  <si>
+    <t>audio w/o metadata</t>
+  </si>
+  <si>
+    <t>happy path ffprobe no pattern</t>
+  </si>
+  <si>
+    <t>happy path mutagen no pattern</t>
+  </si>
+  <si>
+    <t>tests/ConvertedMusic</t>
+  </si>
+  <si>
+    <t>1 audio file type w/ metadata</t>
+  </si>
+  <si>
+    <t>1 audio file type w/0 metadata</t>
+  </si>
+  <si>
+    <t>fail path with pattern</t>
+  </si>
+  <si>
+    <t>happy path with pattern</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -746,7 +761,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -831,16 +846,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,10 +1205,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
@@ -1229,7 +1237,7 @@
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -1247,12 +1255,12 @@
         <v>26</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
@@ -1270,12 +1278,12 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>29</v>
@@ -1284,40 +1292,40 @@
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>29</v>
@@ -1326,21 +1334,21 @@
         <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
@@ -1349,21 +1357,21 @@
         <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
@@ -1372,21 +1380,21 @@
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
@@ -1395,19 +1403,19 @@
         <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>29</v>
@@ -1416,40 +1424,40 @@
         <v>29</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>29</v>
@@ -1458,19 +1466,19 @@
         <v>29</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>29</v>
@@ -1479,42 +1487,42 @@
         <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>29</v>
@@ -1523,19 +1531,19 @@
         <v>29</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>29</v>
@@ -1544,19 +1552,19 @@
         <v>29</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>29</v>
@@ -1565,40 +1573,40 @@
         <v>29</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>29</v>
@@ -1607,13 +1615,13 @@
         <v>29</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -1632,13 +1640,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" customWidth="1"/>
     <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="118.140625" bestFit="1" customWidth="1"/>
@@ -1723,13 +1731,13 @@
         <v>29</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G7" s="6"/>
     </row>
@@ -1753,7 +1761,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1767,7 +1775,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>33</v>
@@ -1904,10 +1912,10 @@
         <v>55</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G15" s="20"/>
     </row>
@@ -1928,10 +1936,10 @@
         <v>56</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1956,34 +1964,38 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30" t="s">
-        <v>62</v>
-      </c>
+      <c r="A18" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17" t="s">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="D19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
@@ -1994,230 +2006,266 @@
         <v>25</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24" t="s">
+      <c r="A21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24" t="s">
-        <v>64</v>
-      </c>
+      <c r="D21" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>68</v>
-      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="20"/>
+        <v>64</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>29</v>
+      </c>
       <c r="C24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="23" t="s">
+        <v>65</v>
+      </c>
       <c r="E24" s="20"/>
       <c r="F24" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="16"/>
+        <v>66</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26" t="s">
+      <c r="A25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>72</v>
-      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
+        <v>69</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>169</v>
+      </c>
       <c r="E26" s="26"/>
       <c r="F26" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="26"/>
+        <v>171</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
+        <v>69</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>170</v>
+      </c>
       <c r="E27" s="26"/>
       <c r="F27" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>76</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="G27" s="30"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="26"/>
+      <c r="F28" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>79</v>
-      </c>
+      <c r="A29" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="21"/>
+      <c r="A30" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="19" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" s="21"/>
-    </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>83</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-    </row>
-    <row r="35" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
+      <c r="A33" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -2225,6 +2273,28 @@
       <c r="E36" s="26"/>
       <c r="F36" s="26"/>
       <c r="G36" s="26"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2438,7 +2508,7 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>29</v>
@@ -2447,19 +2517,19 @@
         <v>29</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>29</v>
@@ -2468,19 +2538,19 @@
         <v>29</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>29</v>
@@ -2489,34 +2559,34 @@
         <v>29</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>154</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>158</v>
       </c>
       <c r="G9" s="29"/>
     </row>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6143D798-F08F-4F44-A9AE-228849954325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C9193-BC8C-4CE3-8D48-7B98631A3917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="183">
   <si>
     <t>package</t>
   </si>
@@ -403,9 +403,6 @@
   </si>
   <si>
     <t>happy path mutagen no pattern</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>happy path with pattern</t>
@@ -589,7 +586,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,6 +600,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -746,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -827,6 +838,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1695,7 +1721,7 @@
         <v>83</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1739,7 +1765,7 @@
         <v>83</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1762,7 +1788,7 @@
         <v>92</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1803,10 +1829,10 @@
         <v>98</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1890,13 +1916,13 @@
         <v>97</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1913,10 +1939,10 @@
         <v>103</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G18" s="22"/>
     </row>
@@ -1927,7 +1953,7 @@
       <c r="B19" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="28" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="18" t="s">
@@ -1946,7 +1972,7 @@
       <c r="B20" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="29" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="25" t="s">
@@ -1963,7 +1989,7 @@
       <c r="B21" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="29" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="25" t="s">
@@ -1987,10 +2013,10 @@
         <v>97</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G22" s="17"/>
     </row>
@@ -2008,7 +2034,7 @@
         <v>103</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>114</v>
@@ -2022,7 +2048,7 @@
       <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="19"/>
@@ -2041,7 +2067,7 @@
       <c r="B25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19"/>
@@ -2098,15 +2124,15 @@
       <c r="B28" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>125</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="27"/>
     </row>
@@ -2117,91 +2143,91 @@
       <c r="B29" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G29" s="27"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="28" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>20</v>
@@ -2211,37 +2237,37 @@
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>116</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>20</v>
@@ -2251,21 +2277,21 @@
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F36" s="18" t="s">
         <v>180</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>181</v>
       </c>
       <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="27"/>
@@ -2275,12 +2301,12 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="28" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="18"/>
@@ -2290,7 +2316,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>20</v>
@@ -2336,7 +2362,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2396,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2404,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2464,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2472,7 +2498,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2509,28 +2535,28 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>20</v>
@@ -2539,40 +2565,40 @@
         <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>20</v>
@@ -2581,13 +2607,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -2616,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2624,7 +2650,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2720,27 +2746,27 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C9193-BC8C-4CE3-8D48-7B98631A3917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0754C42-71FE-4C3D-965B-8FA2E5ADCC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="188">
   <si>
     <t>package</t>
   </si>
@@ -369,9 +369,6 @@
     <t>happy path no pattern</t>
   </si>
   <si>
-    <t>do I even need this any more?? Should I output to file instead of console?</t>
-  </si>
-  <si>
     <t>get_media_tags</t>
   </si>
   <si>
@@ -580,13 +577,31 @@
   </si>
   <si>
     <t>test_load_nay_file_invalid</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk_pattern</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk_invalid_pattern</t>
+  </si>
+  <si>
+    <t>.mp3</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>test_get_metadata_type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,6 +625,18 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -757,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -844,15 +871,21 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1606,7 +1639,7 @@
     <col min="2" max="2" width="12.42578125" style="14" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="14" customWidth="1"/>
     <col min="4" max="4" width="36.85546875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" style="14" customWidth="1"/>
     <col min="6" max="6" width="53.28515625" style="14" customWidth="1"/>
     <col min="7" max="7" width="113.42578125" style="14" customWidth="1"/>
     <col min="8" max="16384" width="8.5703125" style="14"/>
@@ -1721,7 +1754,7 @@
         <v>83</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1765,7 +1798,7 @@
         <v>83</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1788,7 +1821,7 @@
         <v>92</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1829,10 +1862,10 @@
         <v>98</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1916,13 +1949,13 @@
         <v>97</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1939,10 +1972,10 @@
         <v>103</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G18" s="22"/>
     </row>
@@ -1953,17 +1986,17 @@
       <c r="B19" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>13</v>
+      <c r="C19" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="18" t="s">
+        <v>182</v>
+      </c>
       <c r="F19" s="18"/>
-      <c r="G19" s="18" t="s">
-        <v>112</v>
-      </c>
+      <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
@@ -1972,15 +2005,21 @@
       <c r="B20" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="29" t="s">
-        <v>13</v>
+      <c r="C20" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
+      <c r="E20" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
@@ -1989,19 +2028,23 @@
       <c r="B21" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="29" t="s">
-        <v>13</v>
+      <c r="C21" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="E21" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>174</v>
+      </c>
       <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>20</v>
@@ -2013,16 +2056,16 @@
         <v>97</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>20</v>
@@ -2034,73 +2077,75 @@
         <v>103</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="18" t="s">
+      <c r="G24" s="18" t="s">
         <v>116</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>13</v>
+      <c r="C25" s="29" t="s">
+        <v>186</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="27" t="s">
         <v>119</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>120</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="22" t="s">
         <v>121</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B27" s="27" t="s">
         <v>20</v>
@@ -2109,55 +2154,55 @@
         <v>20</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="22"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" s="27"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B29" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G29" s="27"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>20</v>
@@ -2169,65 +2214,65 @@
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>131</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>20</v>
@@ -2237,37 +2282,37 @@
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>20</v>
@@ -2277,21 +2322,21 @@
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="18" t="s">
         <v>179</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>180</v>
       </c>
       <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="27"/>
@@ -2301,7 +2346,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>20</v>
@@ -2316,7 +2361,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>20</v>
@@ -2331,7 +2376,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2362,7 +2407,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2422,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2430,7 +2475,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2490,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2498,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2535,28 +2580,28 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>20</v>
@@ -2565,40 +2610,40 @@
         <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>20</v>
@@ -2607,13 +2652,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -2642,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2650,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2746,27 +2791,27 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -466,7 +466,7 @@
     <t xml:space="preserve">happy path with pattern</t>
   </si>
   <si>
-    <t xml:space="preserve">1 audio file type w/ metadata</t>
+    <t xml:space="preserve">1 audio file type w/ metadata and matching pattern</t>
   </si>
   <si>
     <t xml:space="preserve">doesn’t matter if ffprobe or mutagen, test is about using a pattern</t>
@@ -808,127 +808,127 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1183,478 +1183,478 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="46.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="48.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="45.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="10"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="B24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1675,436 +1675,436 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="23.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="36.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="41.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="53.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="113.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="12" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="23.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="36.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="41.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="53.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="113.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="13" width="8.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="16"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="B8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="22" t="s">
+      <c r="B10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="22" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="19" t="s">
+      <c r="B11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="16" t="s">
+      <c r="B12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" s="12" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="B13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="17" t="s">
+      <c r="B14" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="17" t="s">
+      <c r="B15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="17" t="s">
+      <c r="B16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="18" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="B17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="B18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="B19" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="24" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="23" t="s">
+      <c r="B21" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="B22" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>127</v>
       </c>
       <c r="B23" s="25" t="s">
@@ -2125,51 +2125,51 @@
       <c r="G23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="B24" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="17" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="17" t="s">
+      <c r="B25" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="16"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="15.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>138</v>
       </c>
       <c r="B26" s="26" t="s">
@@ -2184,15 +2184,15 @@
       <c r="E26" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>138</v>
       </c>
       <c r="B27" s="26" t="s">
@@ -2207,13 +2207,13 @@
       <c r="E27" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>138</v>
       </c>
       <c r="B28" s="26" t="s">
@@ -2226,7 +2226,7 @@
         <v>145</v>
       </c>
       <c r="E28" s="26"/>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G28" s="26" t="s">
@@ -2234,7 +2234,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>138</v>
       </c>
       <c r="B29" s="26" t="s">
@@ -2247,7 +2247,7 @@
         <v>148</v>
       </c>
       <c r="E29" s="26"/>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="16" t="s">
         <v>149</v>
       </c>
       <c r="G29" s="26" t="s">
@@ -2255,154 +2255,154 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="19" t="s">
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="20" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="B31" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="16" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="15"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="B33" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G33" s="15"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="17" t="s">
+      <c r="B34" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="17" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G35" s="16"/>
+      <c r="G35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="17" t="s">
+      <c r="B36" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="17"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>169</v>
       </c>
       <c r="B37" s="26" t="s">
@@ -2417,22 +2417,22 @@
       <c r="G37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="16" t="s">
         <v>171</v>
       </c>
       <c r="B39" s="26" t="s">
@@ -2465,60 +2465,60 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2541,60 +2541,60 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2617,36 +2617,36 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="35.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="46.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2675,46 +2675,46 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
@@ -2777,60 +2777,60 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2853,76 +2853,76 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>197</v>
       </c>
     </row>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E37DBE-27B0-4877-AA81-7752FC50D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2F4058-98B7-42AC-8592-52F3176B5E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -686,12 +686,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -912,14 +910,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2279,8 +2277,8 @@
       <c r="B31" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="26" t="s">
-        <v>13</v>
+      <c r="C31" s="28" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>101</v>
@@ -2670,25 +2668,25 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="26" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2735,46 +2733,46 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="B8" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="28"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="B9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1803DAE-0913-4018-A0F1-9CBD9D603C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06972641-008B-4B03-B80C-D7AC78B8CE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="269">
   <si>
     <t>package</t>
   </si>
@@ -366,18 +366,9 @@
     <t>valid audio w/ metadata: m4a, mp3, wma</t>
   </si>
   <si>
-    <t>calls load_any_file. Happy path with all 3 audio file types.</t>
-  </si>
-  <si>
     <t>fail path</t>
   </si>
   <si>
-    <t>test_get_any_tags_invalid_file</t>
-  </si>
-  <si>
-    <t>non-audio file</t>
-  </si>
-  <si>
     <t>test_get_any_tags_wo_metadata</t>
   </si>
   <si>
@@ -790,13 +781,70 @@
   </si>
   <si>
     <t>__loudnorm_json_parse</t>
+  </si>
+  <si>
+    <t>test_ebu_normalize_dynamic</t>
+  </si>
+  <si>
+    <t>test_ebu_normalize_linear</t>
+  </si>
+  <si>
+    <t>test_get_bit_rate</t>
+  </si>
+  <si>
+    <t>test_get_sample_rate</t>
+  </si>
+  <si>
+    <t>test_get_volume_info</t>
+  </si>
+  <si>
+    <t>test_get_volume_info_fail</t>
+  </si>
+  <si>
+    <t>test_peak_normalize_file</t>
+  </si>
+  <si>
+    <t>test_peak_normalize_file_clipping</t>
+  </si>
+  <si>
+    <t>test_peak_normalize_file_max_volume</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_file</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_file_clipping</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_max_volume</t>
+  </si>
+  <si>
+    <t>Abba-Waterloo.mp3</t>
+  </si>
+  <si>
+    <t>happy path dynamic ebu r128</t>
+  </si>
+  <si>
+    <t>happy path linear ebu r128</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>this is really a SubprocessUtilities.popen_pipe test, adapt for test_subprocess_utilities</t>
+  </si>
+  <si>
+    <t>this is really a SubprocessUtilities.subprocess_run test, adapt for test_subprocess_utilities</t>
+  </si>
+  <si>
+    <t>calls load_any_file. Happy path with all 3 audio file types. Fail test not needed, as load any file is actually error source.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -822,6 +870,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -917,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1039,6 +1094,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1784,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="5" customWidth="1"/>
@@ -2061,7 +2119,7 @@
         <v>110</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>111</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2075,51 +2133,53 @@
         <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" s="11" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="B17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>20</v>
+      <c r="C18" s="42" t="s">
+        <v>265</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>119</v>
@@ -2127,53 +2187,53 @@
       <c r="F18" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="B19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="F20" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>20</v>
@@ -2182,105 +2242,109 @@
         <v>20</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="G21" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="17"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="10" t="s">
+      <c r="B22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>117</v>
-      </c>
+      <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" s="9"/>
+      <c r="G23" s="9" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="D24" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="18" t="s">
+      <c r="B25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="18"/>
+      <c r="G25" s="10" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>20</v>
@@ -2289,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>139</v>
@@ -2297,34 +2361,34 @@
       <c r="F26" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="11" t="s">
+      <c r="B27" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="E27" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="10"/>
+      <c r="F27" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>20</v>
@@ -2333,21 +2397,21 @@
         <v>20</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="19" t="s">
         <v>148</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>20</v>
@@ -2356,67 +2420,67 @@
         <v>20</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="19" t="s">
+      <c r="A30" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="B30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="10" t="s">
         <v>155</v>
       </c>
+      <c r="G30" s="13" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="B31" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>159</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>20</v>
@@ -2425,21 +2489,19 @@
         <v>20</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" s="9" t="s">
         <v>164</v>
       </c>
+      <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>20</v>
@@ -2448,63 +2510,63 @@
         <v>20</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="9" t="s">
+      <c r="B34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G34" s="9"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>171</v>
-      </c>
       <c r="F35" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>172</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>20</v>
@@ -2513,99 +2575,78 @@
         <v>20</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G36" s="10"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="11" t="s">
+      <c r="B37" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="19" t="s">
+      <c r="B38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G38" s="19"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="B39" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G39" s="10"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="G40" s="19"/>
+      <c r="G39" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2641,7 +2682,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2699,7 +2740,7 @@
     </row>
     <row r="7" spans="1:7" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>20</v>
@@ -2708,19 +2749,19 @@
         <v>20</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G7" s="34"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>20</v>
@@ -2729,40 +2770,40 @@
         <v>20</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G8" s="34"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>189</v>
-      </c>
       <c r="F9" s="37" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G9" s="34"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>20</v>
@@ -2771,19 +2812,19 @@
         <v>20</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G10" s="34"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>20</v>
@@ -2792,19 +2833,19 @@
         <v>20</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G11" s="36"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B12" s="36" t="s">
         <v>20</v>
@@ -2813,19 +2854,19 @@
         <v>20</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G12" s="36"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>13</v>
@@ -2843,7 +2884,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2854,15 +2895,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2871,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2879,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2937,10 +2978,14 @@
     </row>
     <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
+        <v>249</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>13</v>
+      </c>
       <c r="D7" s="27"/>
       <c r="E7" s="27"/>
       <c r="F7" s="27"/>
@@ -2948,80 +2993,216 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="28"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
+      <c r="B12" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="27"/>
+        <v>195</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>20</v>
+      </c>
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
+      <c r="E13" s="27" t="s">
+        <v>255</v>
+      </c>
       <c r="F13" s="27"/>
       <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="28"/>
+        <v>196</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>20</v>
+      </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3048,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3056,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3114,7 +3295,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -3125,7 +3306,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -3136,7 +3317,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -3147,7 +3328,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3158,7 +3339,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -3169,28 +3350,28 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>20</v>
@@ -3199,19 +3380,19 @@
         <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3222,7 +3403,7 @@
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
@@ -3233,7 +3414,7 @@
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
@@ -3244,7 +3425,7 @@
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -3255,28 +3436,28 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>220</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>223</v>
       </c>
       <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>20</v>
@@ -3285,19 +3466,19 @@
         <v>20</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="27"/>
@@ -3308,7 +3489,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
@@ -3319,7 +3500,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
@@ -3353,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3478,27 +3659,27 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06972641-008B-4B03-B80C-D7AC78B8CE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD6B0C0-7F1A-4366-8340-503F3C75863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="274">
   <si>
     <t>package</t>
   </si>
@@ -63,12 +63,6 @@
     <t>test case</t>
   </si>
   <si>
-    <t>test def</t>
-  </si>
-  <si>
-    <t>test inputs</t>
-  </si>
-  <si>
     <t>__init__</t>
   </si>
   <si>
@@ -390,12 +384,6 @@
     <t>PITA to test, each os returns different path sep and anchor/root in filename key/value. Test return dict is not None, x has keys/values and 2 inner dicts with y and z keys/values. Update all installs of ffmpeg</t>
   </si>
   <si>
-    <t>test_get_media_info_invalid_file</t>
-  </si>
-  <si>
-    <t>a m3u (invalide file)</t>
-  </si>
-  <si>
     <t>get_media_info_walk</t>
   </si>
   <si>
@@ -429,9 +417,6 @@
     <t>test_get_media_tags_invalid_file</t>
   </si>
   <si>
-    <t>Non-audio file</t>
-  </si>
-  <si>
     <t>test_get_media_tags_wo_metadata</t>
   </si>
   <si>
@@ -838,13 +823,43 @@
   </si>
   <si>
     <t>calls load_any_file. Happy path with all 3 audio file types. Fail test not needed, as load any file is actually error source.</t>
+  </si>
+  <si>
+    <t>test_get_media_info_regex_no_dict</t>
+  </si>
+  <si>
+    <t>mocks SubprocessUtilities.popen_pipe return string to not have any inner dictionaries for regex to match</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>test name</t>
+  </si>
+  <si>
+    <t>mocks SubprocessUtilities.subprocess_run return process object  to contain invalid json in process.stdout</t>
+  </si>
+  <si>
+    <t>test_get_media_tags_json_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SubprocessUtilities.popen_pipe return string</t>
+  </si>
+  <si>
+    <t>SubprocessUtilities.subprocess_run return process object  stdout</t>
+  </si>
+  <si>
+    <t>test_subprocess_popen_pipe_invalid_file</t>
+  </si>
+  <si>
+    <t>m3u file</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -873,6 +888,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -972,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1031,9 +1052,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1065,9 +1083,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1092,10 +1107,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1395,439 +1410,439 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="B6" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="C6" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="D6" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="36"/>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="38"/>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="B8" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="4" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="B14" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="E14" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="38" t="s">
+      <c r="F14" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="38"/>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
+      <c r="E15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="F16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="B17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+      <c r="F17" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="38" t="s">
+      <c r="G17" s="36"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="38"/>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B19" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="39"/>
-    </row>
-    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="39"/>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="B24" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="E24" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="39" t="s">
+      <c r="F24" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="39"/>
+      <c r="G24" s="37"/>
     </row>
     <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1868,7 +1883,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1884,19 +1899,19 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>9</v>
+        <v>266</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>4</v>
@@ -1904,747 +1919,747 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>78</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="14" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="16" t="s">
+      <c r="F11" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>93</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="G12" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="F14" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="G14" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="G15" s="10" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="G17" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>265</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>267</v>
+        <v>124</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>133</v>
-      </c>
       <c r="F24" s="18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>146</v>
-      </c>
       <c r="E28" s="19" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="E32" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G33" s="9"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G39" s="19"/>
     </row>
@@ -2659,232 +2674,232 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="69.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.5703125" style="31"/>
+    <col min="1" max="1" width="18.5703125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="29" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="69.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7" spans="1:7" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="32"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="F10" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" s="32"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="G12" s="34"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="33"/>
-    </row>
-    <row r="7" spans="1:7" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="G10" s="34"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="G11" s="36"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="G12" s="36"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>235</v>
+      <c r="D13" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2912,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2920,7 +2935,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2932,277 +2947,277 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="26"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="G8" s="28"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="B15" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="28"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="B16" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="27"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27" t="s">
+      <c r="B18" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27" t="s">
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27" t="s">
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3229,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3237,7 +3252,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,53 +3264,53 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="21"/>
+      <c r="D6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -3305,30 +3320,30 @@
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="A8" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
+      <c r="A9" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3339,7 +3354,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -3350,49 +3365,49 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3402,30 +3417,30 @@
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
+      <c r="A15" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
+      <c r="A16" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>216</v>
+      <c r="A17" s="21" t="s">
+        <v>211</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -3435,79 +3450,79 @@
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="26" t="s">
+      <c r="F19" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="G18" s="26"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="26" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="G19" s="26"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3517,16 +3532,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="79.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3534,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3542,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3554,49 +3569,95 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>262</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3648,10 +3709,10 @@
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>4</v>
@@ -3659,27 +3720,27 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE54A01-5277-4E35-9528-E33161692B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E6253F-F945-4F58-B1B4-159F4FEB1757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,17 @@
     <sheet name="SubprocessUtilities" sheetId="6" r:id="rId6"/>
     <sheet name="Main" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -31,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="302">
   <si>
     <t>package</t>
   </si>
@@ -48,9 +57,6 @@
     <t>comments</t>
   </si>
   <si>
-    <t>file exist/not exist tests handled by main.py tests</t>
-  </si>
-  <si>
     <t>function</t>
   </si>
   <si>
@@ -849,15 +855,6 @@
     <t>this is really a SubprocessUtilities.subprocess_run test, adapt for test_subprocess_utilities</t>
   </si>
   <si>
-    <t>test needed</t>
-  </si>
-  <si>
-    <t>test case</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>one test for file existance</t>
   </si>
   <si>
@@ -888,12 +885,6 @@
     <t>fail path file already loud enough</t>
   </si>
   <si>
-    <t>Crush-Live.mp3,?? In "ConvertedMusic"</t>
-  </si>
-  <si>
-    <t>need file that can be rms normalized. Not pattern match type func</t>
-  </si>
-  <si>
     <t>happy path ebu normalizing</t>
   </si>
   <si>
@@ -916,6 +907,45 @@
   </si>
   <si>
     <t>subprocess_run will throw CalledProcessError</t>
+  </si>
+  <si>
+    <t>look at metadata test for example</t>
+  </si>
+  <si>
+    <t>file that will clip</t>
+  </si>
+  <si>
+    <t>mock the created file</t>
+  </si>
+  <si>
+    <t>remove getter/setter. Never been used.</t>
+  </si>
+  <si>
+    <t>mock subprocess_run ret val. Refer to metadata tests for how to test private def.</t>
+  </si>
+  <si>
+    <t>mocked input</t>
+  </si>
+  <si>
+    <t>file that will max vol fail</t>
+  </si>
+  <si>
+    <t>Taming of Smeagol.mp3</t>
+  </si>
+  <si>
+    <t>Crush-Live.mp3 in "ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>Taming of Smeagol in "ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>Not pattern match type func</t>
+  </si>
+  <si>
+    <t>Can be dynamic or linear. Not pattern match type func</t>
+  </si>
+  <si>
+    <t>will have to mock the clip amount to force clip guard</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1167,6 +1197,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1428,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
@@ -1456,453 +1494,445 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="5"/>
+      <c r="D6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="5" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="7" t="s">
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="6" t="s">
+    <row r="23" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1912,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="8" customWidth="1"/>
@@ -1938,785 +1968,777 @@
         <v>2</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="15"/>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="B6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="F6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>282</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="A10" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="B10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="17" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>92</v>
+        <v>19</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="B13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="E14" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>102</v>
-      </c>
       <c r="B15" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="E17" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G18" s="15" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>116</v>
       </c>
+      <c r="B18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>20</v>
+        <v>116</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>118</v>
+        <v>19</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>94</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="14"/>
+      <c r="F19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="41"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="41"/>
+      <c r="F20" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="18" t="s">
+      <c r="A21" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G21" s="41" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>20</v>
+        <v>123</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>19</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F22" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="15" t="s">
         <v>129</v>
       </c>
+      <c r="F23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="42"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="19" t="s">
+      <c r="A24" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G24" s="42"/>
+      <c r="B24" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="43" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E28" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>145</v>
-      </c>
       <c r="G28" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="15" t="s">
+      <c r="A29" s="11" t="s">
         <v>149</v>
       </c>
+      <c r="B29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="A30" s="10" t="s">
         <v>153</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>158</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F33" s="10" t="s">
+      <c r="A33" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G33" s="15"/>
+      <c r="B33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>166</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>167</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="14"/>
+        <v>168</v>
+      </c>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="F36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G36" s="13"/>
+      <c r="B36" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G36" s="43"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="20" t="s">
+      <c r="A37" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="G37" s="43"/>
+      <c r="B37" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="A38" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="B38" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="20" t="s">
+      <c r="F38" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="F39" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="G39" s="43"/>
+      <c r="G38" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2726,7 +2748,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" style="21" customWidth="1"/>
@@ -2752,209 +2774,201 @@
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="24"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G7" s="24"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G8" s="24"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G9" s="24"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="G10" s="24"/>
+      <c r="B10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="27" t="s">
+      <c r="A12" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="G12" s="27"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="B12" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="24" t="s">
         <v>200</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="1" customWidth="1"/>
@@ -2974,7 +2988,7 @@
     <col min="4" max="4" width="31.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="37.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="76.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="85" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2990,498 +3004,516 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="10"/>
+      <c r="B6" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+      <c r="F7" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="29" t="s">
+      <c r="F8" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
+      <c r="B9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>211</v>
+        <v>44</v>
       </c>
       <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="A11" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="31"/>
+      <c r="B11" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="29"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="29"/>
+        <v>217</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="F13" s="29" t="s">
+      <c r="A13" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="G13" s="29"/>
+      <c r="B13" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>220</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="G14" s="31"/>
+        <v>217</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>221</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="G15" s="31"/>
+        <v>217</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="31" t="s">
+      <c r="A16" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="G16" s="31"/>
+      <c r="B16" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E17" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="29"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>294</v>
+      <c r="B18" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>286</v>
-      </c>
+      <c r="B21" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>99</v>
+        <v>279</v>
       </c>
       <c r="E22" s="29" t="s">
         <v>227</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="29"/>
+        <v>290</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E23" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="F23" s="29"/>
+      <c r="F23" s="29" t="s">
+        <v>229</v>
+      </c>
       <c r="G23" s="29"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="F24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="G24" s="29"/>
+      <c r="B24" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>99</v>
+        <v>279</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="F25" s="31"/>
+      <c r="F25" s="31" t="s">
+        <v>44</v>
+      </c>
       <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E26" s="31" t="s">
         <v>233</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
       <c r="G26" s="31"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3491,7 +3523,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" style="1" customWidth="1"/>
@@ -3500,7 +3532,7 @@
     <col min="4" max="4" width="35.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="31.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="46.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="67.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3508,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,94 +3548,101 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="32"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
@@ -3616,177 +3655,178 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="A13" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-    </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="B17" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G18" s="36"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="36" t="s">
+      <c r="A19" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="G19" s="36"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
+      <c r="B21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3796,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
@@ -3813,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3821,106 +3861,98 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="10"/>
+      <c r="B6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>215</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>267</v>
-      </c>
       <c r="G7" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3931,14 +3963,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" customWidth="1"/>
   </cols>
@@ -3953,59 +3985,84 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="38" t="s">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="38" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46" t="s">
         <v>273</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="F5" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" t="s">
-        <v>279</v>
-      </c>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E9792C-919B-4A5C-8A2A-F3B1E70CCABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AudioArt" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="AudioMetadata" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="AudioPlaylist" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="AudioNormalization" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="DirectoryProcessing" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="SubprocessUtilities" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Main" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
+    <sheet name="AudioMetadata" sheetId="2" r:id="rId2"/>
+    <sheet name="AudioPlaylist" sheetId="3" r:id="rId3"/>
+    <sheet name="AudioNormalization" sheetId="4" r:id="rId4"/>
+    <sheet name="DirectoryProcessing" sheetId="5" r:id="rId5"/>
+    <sheet name="SubprocessUtilities" sheetId="6" r:id="rId6"/>
+    <sheet name="Main" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,949 +31,919 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="304">
-  <si>
-    <t xml:space="preserve">package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">written</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">__init__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">__unpack_asf_image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gets called by extract_asf_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">__write_data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gets called by extract_asf/m4a/mp3_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_album_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract album art from file that already has co-located Folder.jpg file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_album_art_folder_exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABBA-Waterloo.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract album art from non-valid file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_album_art_invalid_audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.m3u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art file w/o tags or stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_album_art_no_tag_or_stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No_tag_Crush-Live.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensures both primary &amp; sec extraction will fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art file with stream &amp; tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_album_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elton John-Saturday Night's Alright for Fighting.wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art file w/o stream and with tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_album_art_without_stream_with_tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billie Holdiay-Georgia On My Mind.wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensure pri method fail and sec method passes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_asf_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art from asf/wma file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_asf_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_ffmpeg_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art from valid audio file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_ffmpeg_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crush-Live.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract art from valid audio file w/o stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_ffmpeg_art_no_stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_m4a_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_m4a_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua Davis-Workingmans's Hymn.m4a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_mp3_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_mp3_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract walk without a pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m4a/mp3/wma w embedded in testSetup built "PreppedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern valid/invalid tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract walk with a pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_walk_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.mp3 w embedded in testSetup built "PreppedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extract walk with invalid pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_extract_walk_invalid_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.m3u with testSetup built "PreppedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_video_stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio file does not have video stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_has_video_stream_false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio file has a video stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_has_video_stream_true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set_album_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set album art for album dirs, 1 Folder .jpg exists, 1 folder .jpg copied from AlbumArt, rest of albums no album art set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_set_album_art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio_metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_update_id3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">update tags with max unique date and setting tpos value if necessary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_update_id3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set of unique date strings &amp; tag dict w/o TPOS and with TYER = 1900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">convert_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path - valid audio files w/Folder.jpgs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info.  Test support fuinctions seperately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid audio files w/o co-located folder.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_file_no_jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp3 w/o co-located Folder.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid audio file w/o co-located folder.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_file_wo_metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp3 w/o metada and w co-located Folder.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">convert_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path - no pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no pattern (will do all mp3, m4a, wma files), confirm output mp3 files exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path - valid pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_walk_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m4a/mp3/wma with co-located Folder.jpgs in "tests/ConvertedMusic", call with .mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one  pattern is fine, test is all about acceptting a valid pattern input.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invalid pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_convert_walk_pattern_invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">call with .m3u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_album_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_create_album_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select audio file from test/Music, move to  testSetup built PreppedMusic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls get_media_tags, make_album_dir, move_audio_file, create_csv. Test support functions seperately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_any_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_any_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid audio w/ metadata: m4a, mp3, wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls load_any_file. Happy path with all 3 audio file types. Fail test not needed, as load any file is actually error source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_any_tags_wo_metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid audio w/o metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">only need to test with one audio file type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_media_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a mp3 with valid metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PITA to test, each os returns different path sep and anchor/root in filename key/value. Test return dict is not None, x has keys/values and 2 inner dicts with y and z keys/values. Update all installs of ffmpeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_info_regex_no_dict</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="300">
+  <si>
+    <t>package</t>
+  </si>
+  <si>
+    <t>src.info</t>
+  </si>
+  <si>
+    <t>module</t>
+  </si>
+  <si>
+    <t>audio_art</t>
+  </si>
+  <si>
+    <t>function</t>
+  </si>
+  <si>
+    <t>needed</t>
+  </si>
+  <si>
+    <t>written</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>test name</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>__init__</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>__unpack_asf_image</t>
+  </si>
+  <si>
+    <t>gets called by extract_asf_art</t>
+  </si>
+  <si>
+    <t>__write_data</t>
+  </si>
+  <si>
+    <t>gets called by extract_asf/m4a/mp3_art</t>
+  </si>
+  <si>
+    <t>extract_album_art</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>extract album art from file that already has co-located Folder.jpg file</t>
+  </si>
+  <si>
+    <t>test_extract_album_art_folder_exists</t>
+  </si>
+  <si>
+    <t>ABBA-Waterloo.jpg</t>
+  </si>
+  <si>
+    <t>extract album art from non-valid file</t>
+  </si>
+  <si>
+    <t>test_extract_album_art_invalid_audio</t>
+  </si>
+  <si>
+    <t>test.m3u</t>
+  </si>
+  <si>
+    <t>extract art file w/o tags or stream</t>
+  </si>
+  <si>
+    <t>test_extract_album_art_no_tag_or_stream</t>
+  </si>
+  <si>
+    <t>No_tag_Crush-Live.mp3</t>
+  </si>
+  <si>
+    <t>ensures both primary &amp; sec extraction will fail</t>
+  </si>
+  <si>
+    <t>extract art file with stream &amp; tag</t>
+  </si>
+  <si>
+    <t>test_extract_album_art</t>
+  </si>
+  <si>
+    <t>Elton John-Saturday Night's Alright for Fighting.wma</t>
+  </si>
+  <si>
+    <t>normal case</t>
+  </si>
+  <si>
+    <t>extract art file w/o stream and with tag</t>
+  </si>
+  <si>
+    <t>test_extract_album_art_without_stream_with_tag</t>
+  </si>
+  <si>
+    <t>Billie Holdiay-Georgia On My Mind.wma</t>
+  </si>
+  <si>
+    <t>ensure pri method fail and sec method passes</t>
+  </si>
+  <si>
+    <t>extract_asf_art</t>
+  </si>
+  <si>
+    <t>extract art from asf/wma file</t>
+  </si>
+  <si>
+    <t>test_extract_asf_art</t>
+  </si>
+  <si>
+    <t>extract_ffmpeg_art</t>
+  </si>
+  <si>
+    <t>extract art from valid audio file</t>
+  </si>
+  <si>
+    <t>test_extract_ffmpeg_art</t>
+  </si>
+  <si>
+    <t>Crush-Live.mp3</t>
+  </si>
+  <si>
+    <t>extract art from valid audio file w/o stream</t>
+  </si>
+  <si>
+    <t>test_extract_ffmpeg_art_no_stream</t>
+  </si>
+  <si>
+    <t>extract_m4a_art</t>
+  </si>
+  <si>
+    <t>test_extract_m4a_art</t>
+  </si>
+  <si>
+    <t>Joshua Davis-Workingmans's Hymn.m4a</t>
+  </si>
+  <si>
+    <t>extract_mp3_art</t>
+  </si>
+  <si>
+    <t>test_extract_mp3_art</t>
+  </si>
+  <si>
+    <t>extract_walk</t>
+  </si>
+  <si>
+    <t>extract walk without a pattern</t>
+  </si>
+  <si>
+    <t>test_extract_walk</t>
+  </si>
+  <si>
+    <t>m4a/mp3/wma w embedded in testSetup built "PreppedMusic"</t>
+  </si>
+  <si>
+    <t>pattern valid/invalid tests</t>
+  </si>
+  <si>
+    <t>extract walk with a pattern</t>
+  </si>
+  <si>
+    <t>test_extract_walk_pattern</t>
+  </si>
+  <si>
+    <t>.mp3 w embedded in testSetup built "PreppedMusic"</t>
+  </si>
+  <si>
+    <t>extract walk with invalid pattern</t>
+  </si>
+  <si>
+    <t>test_extract_walk_invalid_pattern</t>
+  </si>
+  <si>
+    <t>.m3u with testSetup built "PreppedMusic"</t>
+  </si>
+  <si>
+    <t>has_video_stream</t>
+  </si>
+  <si>
+    <t>audio file does not have video stream</t>
+  </si>
+  <si>
+    <t>test_has_video_stream_false</t>
+  </si>
+  <si>
+    <t>audio file has a video stream</t>
+  </si>
+  <si>
+    <t>test_has_video_stream_true</t>
+  </si>
+  <si>
+    <t>set_album_art</t>
+  </si>
+  <si>
+    <t>set album art for album dirs, 1 Folder .jpg exists, 1 folder .jpg copied from AlbumArt, rest of albums no album art set</t>
+  </si>
+  <si>
+    <t>test_set_album_art</t>
+  </si>
+  <si>
+    <t>in tests/Music, 1 album dir w Folder.jpg, 1 album dir with jpg in AlbumArt, rest of album dirs w/o Folder.jpg</t>
+  </si>
+  <si>
+    <t>audio_metadata</t>
+  </si>
+  <si>
+    <t>_update_id3</t>
+  </si>
+  <si>
+    <t>update tags with max unique date and setting tpos value if necessary</t>
+  </si>
+  <si>
+    <t>test_update_id3</t>
+  </si>
+  <si>
+    <t>set of unique date strings &amp; tag dict w/o TPOS and with TYER = 1900</t>
+  </si>
+  <si>
+    <t>convert_file</t>
+  </si>
+  <si>
+    <t>happy path - valid audio files w/Folder.jpgs</t>
+  </si>
+  <si>
+    <t>test_convert_file</t>
+  </si>
+  <si>
+    <t>m4a, mp3, wma all with co-located Folder.jpg in testSetup created "tests/ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>calls  path_info, make_dir,  get_metadata_type, get_m4a/mp3/wma_tags, map_m4a/mp3/wma_tags, __update_id3, get_media_info.  Test support fuinctions seperately.</t>
+  </si>
+  <si>
+    <t>valid audio files w/o co-located folder.jpg</t>
+  </si>
+  <si>
+    <t>test_convert_file_no_jpg</t>
+  </si>
+  <si>
+    <t>mp3 w/o co-located Folder.jpg</t>
+  </si>
+  <si>
+    <t>valid audio file w/o co-located folder.jpg</t>
+  </si>
+  <si>
+    <t>test_convert_file_wo_metadata</t>
+  </si>
+  <si>
+    <t>mp3 w/o metada and w co-located Folder.jpg</t>
+  </si>
+  <si>
+    <t>convert_walk</t>
+  </si>
+  <si>
+    <t>happy path - no pattern</t>
+  </si>
+  <si>
+    <t>test_convert_walk</t>
+  </si>
+  <si>
+    <t>no pattern (will do all mp3, m4a, wma files), confirm output mp3 files exist.</t>
+  </si>
+  <si>
+    <t>happy path - valid pattern</t>
+  </si>
+  <si>
+    <t>test_convert_walk_pattern</t>
+  </si>
+  <si>
+    <t>m4a/mp3/wma with co-located Folder.jpgs in "tests/ConvertedMusic", call with .mp3</t>
+  </si>
+  <si>
+    <t>one  pattern is fine, test is all about acceptting a valid pattern input.</t>
+  </si>
+  <si>
+    <t>invalid pattern</t>
+  </si>
+  <si>
+    <t>test_convert_walk_pattern_invalid</t>
+  </si>
+  <si>
+    <t>call with .m3u</t>
+  </si>
+  <si>
+    <t>create_album_dir</t>
+  </si>
+  <si>
+    <t>happy path</t>
+  </si>
+  <si>
+    <t>test_create_album_dir</t>
+  </si>
+  <si>
+    <t>select audio file from test/Music, move to  testSetup built PreppedMusic</t>
+  </si>
+  <si>
+    <t>calls get_media_tags, make_album_dir, move_audio_file, create_csv. Test support functions seperately.</t>
+  </si>
+  <si>
+    <t>get_any_tags</t>
+  </si>
+  <si>
+    <t>test_get_any_tags</t>
+  </si>
+  <si>
+    <t>valid audio w/ metadata: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>calls load_any_file. Happy path with all 3 audio file types. Fail test not needed, as load any file is actually error source.</t>
+  </si>
+  <si>
+    <t>fail path</t>
+  </si>
+  <si>
+    <t>test_get_any_tags_wo_metadata</t>
+  </si>
+  <si>
+    <t>valid audio w/o metadata</t>
+  </si>
+  <si>
+    <t>only need to test with one audio file type</t>
+  </si>
+  <si>
+    <t>get_media_info</t>
+  </si>
+  <si>
+    <t>test_get_media_info</t>
+  </si>
+  <si>
+    <t>a mp3 with valid metadata</t>
+  </si>
+  <si>
+    <t>PITA to test, each os returns different path sep and anchor/root in filename key/value. Test return dict is not None, x has keys/values and 2 inner dicts with y and z keys/values. Update all installs of ffmpeg</t>
+  </si>
+  <si>
+    <t>test_get_media_info_regex_no_dict</t>
   </si>
   <si>
     <t xml:space="preserve"> SubprocessUtilities.popen_pipe return string</t>
   </si>
   <si>
-    <t xml:space="preserve">mocks SubprocessUtilities.popen_pipe return string to not have any inner dictionaries for regex to match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_media_info_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path no pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_info_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_info_walk_invalid_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a m3u (invalid file)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_info_walk_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_media_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio w metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_tags_json_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SubprocessUtilities.subprocess_run return process object  stdout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mocks SubprocessUtilities.subprocess_run return process object  to contain invalid json in process.stdout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_media_tags_wo_metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio w/o metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_metadata_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_metadata_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid audio: m4a, mp3, wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls load_any_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_metadata_type_fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invalid file type m3u?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_tags_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path with pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_tags_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 audio file type w/ metadata and matching pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">doesn’t matter if ffprobe or mutagen, test is about using a pattern, tags retrieval type(ffprobe or mutagen) doesn’t matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path ffprobe no pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_tags_walk_ffprobe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/ConvertedMusic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testing is dual purpose: walk function, w/o pattern, and finally use ffprobe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path mutagen no pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_tags_walk_mutagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testing is dual purpose: walk function, w/o a pattern, and finally use  mutagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_unique_media_keys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_unique_media_keys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/Music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls get_media_tags. Only need to check on existance of output file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_art_tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path audio with embedded art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_has_art_tag_true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">with art tag: m4a, mp3, wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calls get_any_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path audio w/o embedded art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_has_art_tag_false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">without art tag: m4a, mp3, wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_has_art_tag_invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not an audio file: m3u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">load_any_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_load_any_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">add a valid audio file check to code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_load_any_file_invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_load_any_file_non_extant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">file doesn't exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">map_m4a_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_map_m4a_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m4a w metadata from tests/Music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">map_mp3_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_map_mp3_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp3 w metadate from tests/Music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">map_wma_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_map_wma_tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wma w metadata from tests/Music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio_playlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_audio_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path getting audio file name from a m3u #EXTINF line without delimiter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_audio_name_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"#EXTINF:0The Eagles-Desperado.m4a"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path getting m4a audio file name from a m3u #EXTINF line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_audio_name_m4a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"#EXTINF:0,The Eagles-Desperado.m4a"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy pathgetting mp3 audio file name from a m3u #EXTINF line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_audio_name_mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"#EXTINF:0,Sawyer Fredricks - Shots Fired.mp3"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path getting wma audio file name from a m3u #EXTINF line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_audio_name_wma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"#EXTINF:0,Creedence Clearwater Revival-Fortunate Son.wma"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">update_paths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path updating a playlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_update_paths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/Music/test.m3u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path updating a playlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_update_paths_fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/Music/Crush/Here/Crush-Live.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">update_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trivial case, sanity testing suffices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src.audio_normalize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio_normalization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">__loudnorm_json_parse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_loudnorm_json_parse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mocked input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mock subprocess_run ret val. Refer to metadata tests for how to test private def.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_loudnorm_json_parse_decode_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_loudnorm_json_parse_output_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebu_normalize_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path dynamic ebu r128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_ebu_normalize_dynamic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abba-Waterloo.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path linear ebu r128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_ebu_normalize_linear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_bit_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_bit_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_bit_rate_decode_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mocked subprocess_run ret val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_bit_rate_index_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mock AudioNormalization with side effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">side effect is IndexError</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_sample_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_sample_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get-sample_rate_decode_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_sample_rate_index_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_volume_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_volume_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_volume_info_invalid_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subprocess_run will throw CalledProcessError</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normalize_walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path ebu normalizing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_normalize_walk_ebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crush-Live.mp3 in "ConvertedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can be dynamic or linear. Not pattern match type func</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path peak normalizing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_normalize_walk_peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not pattern match type func</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path rms normalizing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_normalize_walk_rms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taming of Smeagol in "ConvertedMusic"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peak_normalize_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_peak_normalize_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path file would clip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_peak_normalize_file_clipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">will have to mock the clip amount to force clip guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path file already loud enough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_peak_normalize_file_max_volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X Ambassadors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rms_normalize_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_rms_normalize_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taming of Smeagol.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_rms_normalize_file_clipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_rms_normalize_max_volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">file that will max vol fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src.dir_processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">directory_processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">__ext_file_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mock the created file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_audio_file_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_ext_file_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_file_directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">happy path find directory path of file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_file_directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio file &lt;tld&gt;/&lt;artist&gt;/&lt;album&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail path not find directory path of file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_get_file_directory_none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">audio file &lt;tld&gt;/&lt;artist&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get_file_ext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">make_album_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">make_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_audio_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get path for audio file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_path_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">joshua davis m4a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get path for non-audio file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_path_info_not_audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected.m3u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remove_album_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remove_pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tld_path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remove getter/setter. Never been used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subprocess_utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">popen_pipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_subprocess_popen_pipe_invalid_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m3u file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is really a SubprocessUtilities.popen_pipe test, adapt for test_subprocess_utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subprocess_run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_subprocess_run_invalid_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is really a SubprocessUtilities.subprocess_run test, adapt for test_subprocess_utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one test for file existance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one test for file non existance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one test for audio file is accpetable type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one test for playlist file is acceptable type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test for extract walk valid/invalide pattern</t>
+    <t>mocks SubprocessUtilities.popen_pipe return string to not have any inner dictionaries for regex to match</t>
+  </si>
+  <si>
+    <t>get_media_info_walk</t>
+  </si>
+  <si>
+    <t>happy path no pattern</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk_invalid_pattern</t>
+  </si>
+  <si>
+    <t>a m3u (invalid file)</t>
+  </si>
+  <si>
+    <t>test_get_media_info_walk_pattern</t>
+  </si>
+  <si>
+    <t>.mp3</t>
+  </si>
+  <si>
+    <t>get_media_tags</t>
+  </si>
+  <si>
+    <t>test_get_media_tags</t>
+  </si>
+  <si>
+    <t>audio w metadata</t>
+  </si>
+  <si>
+    <t>test_get_media_tags_json_error</t>
+  </si>
+  <si>
+    <t>SubprocessUtilities.subprocess_run return process object  stdout</t>
+  </si>
+  <si>
+    <t>mocks SubprocessUtilities.subprocess_run return process object  to contain invalid json in process.stdout</t>
+  </si>
+  <si>
+    <t>test_get_media_tags_wo_metadata</t>
+  </si>
+  <si>
+    <t>audio w/o metadata</t>
+  </si>
+  <si>
+    <t>get_metadata_type</t>
+  </si>
+  <si>
+    <t>test_get_metadata_type</t>
+  </si>
+  <si>
+    <t>valid audio: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>calls load_any_file</t>
+  </si>
+  <si>
+    <t>test_get_metadata_type_fail</t>
+  </si>
+  <si>
+    <t>invalid file type m3u?</t>
+  </si>
+  <si>
+    <t>get_tags_walk</t>
+  </si>
+  <si>
+    <t>happy path with pattern</t>
+  </si>
+  <si>
+    <t>test_get_tags_walk</t>
+  </si>
+  <si>
+    <t>1 audio file type w/ metadata and matching pattern</t>
+  </si>
+  <si>
+    <t>doesn’t matter if ffprobe or mutagen, test is about using a pattern, tags retrieval type(ffprobe or mutagen) doesn’t matter</t>
+  </si>
+  <si>
+    <t>happy path ffprobe no pattern</t>
+  </si>
+  <si>
+    <t>test_get_tags_walk_ffprobe</t>
+  </si>
+  <si>
+    <t>tests/ConvertedMusic</t>
+  </si>
+  <si>
+    <t>testing is dual purpose: walk function, w/o pattern, and finally use ffprobe</t>
+  </si>
+  <si>
+    <t>happy path mutagen no pattern</t>
+  </si>
+  <si>
+    <t>test_get_tags_walk_mutagen</t>
+  </si>
+  <si>
+    <t>testing is dual purpose: walk function, w/o a pattern, and finally use  mutagen</t>
+  </si>
+  <si>
+    <t>get_unique_media_keys</t>
+  </si>
+  <si>
+    <t>test_get_unique_media_keys</t>
+  </si>
+  <si>
+    <t>tests/Music</t>
+  </si>
+  <si>
+    <t>calls get_media_tags. Only need to check on existance of output file.</t>
+  </si>
+  <si>
+    <t>has_art_tag</t>
+  </si>
+  <si>
+    <t>happy path audio with embedded art</t>
+  </si>
+  <si>
+    <t>test_has_art_tag_true</t>
+  </si>
+  <si>
+    <t>with art tag: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>calls get_any_tags</t>
+  </si>
+  <si>
+    <t>happy path audio w/o embedded art</t>
+  </si>
+  <si>
+    <t>test_has_art_tag_false</t>
+  </si>
+  <si>
+    <t>without art tag: m4a, mp3, wma</t>
+  </si>
+  <si>
+    <t>test_has_art_tag_invalid</t>
+  </si>
+  <si>
+    <t>not an audio file: m3u</t>
+  </si>
+  <si>
+    <t>load_any_file</t>
+  </si>
+  <si>
+    <t>test_load_any_file</t>
+  </si>
+  <si>
+    <t>add a valid audio file check to code</t>
+  </si>
+  <si>
+    <t>test_load_any_file_invalid</t>
+  </si>
+  <si>
+    <t>test_load_any_file_non_extant</t>
+  </si>
+  <si>
+    <t>file doesn't exist</t>
+  </si>
+  <si>
+    <t>map_m4a_tags</t>
+  </si>
+  <si>
+    <t>test_map_m4a_tags</t>
+  </si>
+  <si>
+    <t>m4a w metadata from tests/Music</t>
+  </si>
+  <si>
+    <t>map_mp3_tags</t>
+  </si>
+  <si>
+    <t>test_map_mp3_tags</t>
+  </si>
+  <si>
+    <t>mp3 w metadate from tests/Music</t>
+  </si>
+  <si>
+    <t>map_wma_tags</t>
+  </si>
+  <si>
+    <t>test_map_wma_tags</t>
+  </si>
+  <si>
+    <t>wma w metadata from tests/Music</t>
+  </si>
+  <si>
+    <t>audio_playlist</t>
+  </si>
+  <si>
+    <t>get_audio_name</t>
+  </si>
+  <si>
+    <t>fail path getting audio file name from a m3u #EXTINF line without delimiter</t>
+  </si>
+  <si>
+    <t>test_get_audio_name_error</t>
+  </si>
+  <si>
+    <t>"#EXTINF:0The Eagles-Desperado.m4a"</t>
+  </si>
+  <si>
+    <t>happy path getting m4a audio file name from a m3u #EXTINF line</t>
+  </si>
+  <si>
+    <t>test_get_audio_name_m4a</t>
+  </si>
+  <si>
+    <t>"#EXTINF:0,The Eagles-Desperado.m4a"</t>
+  </si>
+  <si>
+    <t>happy pathgetting mp3 audio file name from a m3u #EXTINF line</t>
+  </si>
+  <si>
+    <t>test_get_audio_name_mp3</t>
+  </si>
+  <si>
+    <t>"#EXTINF:0,Sawyer Fredricks - Shots Fired.mp3"</t>
+  </si>
+  <si>
+    <t>happy path getting wma audio file name from a m3u #EXTINF line</t>
+  </si>
+  <si>
+    <t>test_get_audio_name_wma</t>
+  </si>
+  <si>
+    <t>"#EXTINF:0,Creedence Clearwater Revival-Fortunate Son.wma"</t>
+  </si>
+  <si>
+    <t>update_paths</t>
+  </si>
+  <si>
+    <t>happy path updating a playlist</t>
+  </si>
+  <si>
+    <t>test_update_paths</t>
+  </si>
+  <si>
+    <t>tests/Music/test.m3u</t>
+  </si>
+  <si>
+    <t>fail path updating a playlist</t>
+  </si>
+  <si>
+    <t>test_update_paths_fail</t>
+  </si>
+  <si>
+    <t>tests/Music/Crush/Here/Crush-Live.mp3</t>
+  </si>
+  <si>
+    <t>update_walk</t>
+  </si>
+  <si>
+    <t>trivial case, sanity testing suffices</t>
+  </si>
+  <si>
+    <t>src.audio_normalize</t>
+  </si>
+  <si>
+    <t>audio_normalization</t>
+  </si>
+  <si>
+    <t>__loudnorm_json_parse</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>test_loudnorm_json_parse</t>
+  </si>
+  <si>
+    <t>mocked input</t>
+  </si>
+  <si>
+    <t>mock subprocess_run ret val. Refer to metadata tests for how to test private def.</t>
+  </si>
+  <si>
+    <t>test_loudnorm_json_parse_decode_error</t>
+  </si>
+  <si>
+    <t>test_loudnorm_json_parse_output_error</t>
+  </si>
+  <si>
+    <t>ebu_normalize_file</t>
+  </si>
+  <si>
+    <t>happy path dynamic ebu r128</t>
+  </si>
+  <si>
+    <t>test_ebu_normalize_dynamic</t>
+  </si>
+  <si>
+    <t>Abba-Waterloo.mp3</t>
+  </si>
+  <si>
+    <t>happy path linear ebu r128</t>
+  </si>
+  <si>
+    <t>test_ebu_normalize_linear</t>
+  </si>
+  <si>
+    <t>get_bit_rate</t>
+  </si>
+  <si>
+    <t>test_get_bit_rate</t>
+  </si>
+  <si>
+    <t>test_get_bit_rate_decode_error</t>
+  </si>
+  <si>
+    <t>mocked subprocess_run ret val</t>
+  </si>
+  <si>
+    <t>test_get_bit_rate_index_error</t>
+  </si>
+  <si>
+    <t>Mock AudioNormalization with side effect</t>
+  </si>
+  <si>
+    <t>side effect is IndexError</t>
+  </si>
+  <si>
+    <t>get_sample_rate</t>
+  </si>
+  <si>
+    <t>test_get_sample_rate</t>
+  </si>
+  <si>
+    <t>test_get-sample_rate_decode_error</t>
+  </si>
+  <si>
+    <t>test_get_sample_rate_index_error</t>
+  </si>
+  <si>
+    <t>get_volume_info</t>
+  </si>
+  <si>
+    <t>test_get_volume_info</t>
+  </si>
+  <si>
+    <t>test_get_volume_info_invalid_file</t>
+  </si>
+  <si>
+    <t>subprocess_run will throw CalledProcessError</t>
+  </si>
+  <si>
+    <t>normalize_walk</t>
+  </si>
+  <si>
+    <t>happy path ebu normalizing</t>
+  </si>
+  <si>
+    <t>test_normalize_walk_ebu</t>
+  </si>
+  <si>
+    <t>Crush-Live.mp3 in "ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>Can be dynamic or linear. Not pattern match type func</t>
+  </si>
+  <si>
+    <t>happy path peak normalizing</t>
+  </si>
+  <si>
+    <t>test_normalize_walk_peak</t>
+  </si>
+  <si>
+    <t>Not pattern match type func</t>
+  </si>
+  <si>
+    <t>happy path rms normalizing</t>
+  </si>
+  <si>
+    <t>test_normalize_walk_rms</t>
+  </si>
+  <si>
+    <t>Taming of Smeagol in "ConvertedMusic"</t>
+  </si>
+  <si>
+    <t>peak_normalize_file</t>
+  </si>
+  <si>
+    <t>test_peak_normalize_file</t>
+  </si>
+  <si>
+    <t>fail path file would clip</t>
+  </si>
+  <si>
+    <t>fail path file already loud enough</t>
+  </si>
+  <si>
+    <t>test_peak_normalize_file_max_volume</t>
+  </si>
+  <si>
+    <t>X Ambassadors</t>
+  </si>
+  <si>
+    <t>rms_normalize_file</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_file</t>
+  </si>
+  <si>
+    <t>Taming of Smeagol.mp3</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_file_clipping</t>
+  </si>
+  <si>
+    <t>test_rms_normalize_max_volume</t>
+  </si>
+  <si>
+    <t>src.dir_processing</t>
+  </si>
+  <si>
+    <t>directory_processing</t>
+  </si>
+  <si>
+    <t>__ext_file_list</t>
+  </si>
+  <si>
+    <t>create_csv</t>
+  </si>
+  <si>
+    <t>mock the created file</t>
+  </si>
+  <si>
+    <t>create_txt</t>
+  </si>
+  <si>
+    <t>get_audio_file_list</t>
+  </si>
+  <si>
+    <t>get_ext_file_list</t>
+  </si>
+  <si>
+    <t>get_file_directory</t>
+  </si>
+  <si>
+    <t>happy path find directory path of file</t>
+  </si>
+  <si>
+    <t>test_get_file_directory</t>
+  </si>
+  <si>
+    <t>audio file &lt;tld&gt;/&lt;artist&gt;/&lt;album&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
+  </si>
+  <si>
+    <t>fail path not find directory path of file</t>
+  </si>
+  <si>
+    <t>test_get_file_directory_none</t>
+  </si>
+  <si>
+    <t>audio file &lt;tld&gt;/&lt;artist&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
+  </si>
+  <si>
+    <t>get_file_ext</t>
+  </si>
+  <si>
+    <t>make_album_dir</t>
+  </si>
+  <si>
+    <t>make_dir</t>
+  </si>
+  <si>
+    <t>move_audio_file</t>
+  </si>
+  <si>
+    <t>path_info</t>
+  </si>
+  <si>
+    <t>get path for audio file</t>
+  </si>
+  <si>
+    <t>test_path_info</t>
+  </si>
+  <si>
+    <t>joshua davis m4a</t>
+  </si>
+  <si>
+    <t>get path for non-audio file</t>
+  </si>
+  <si>
+    <t>test_path_info_not_audio</t>
+  </si>
+  <si>
+    <t>expected.m3u</t>
+  </si>
+  <si>
+    <t>remove_album_dir</t>
+  </si>
+  <si>
+    <t>remove_pattern</t>
+  </si>
+  <si>
+    <t>tld_path</t>
+  </si>
+  <si>
+    <t>remove getter/setter. Never been used.</t>
+  </si>
+  <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>subprocess_utilities</t>
+  </si>
+  <si>
+    <t>popen_pipe</t>
+  </si>
+  <si>
+    <t>test_subprocess_popen_pipe_invalid_file</t>
+  </si>
+  <si>
+    <t>m3u file</t>
+  </si>
+  <si>
+    <t>this is really a SubprocessUtilities.popen_pipe test, adapt for test_subprocess_utilities</t>
+  </si>
+  <si>
+    <t>subprocess_run</t>
+  </si>
+  <si>
+    <t>test_subprocess_run_invalid_file</t>
+  </si>
+  <si>
+    <t>this is really a SubprocessUtilities.subprocess_run test, adapt for test_subprocess_utilities</t>
+  </si>
+  <si>
+    <t>one test for file existance</t>
+  </si>
+  <si>
+    <t>one test for file non existance</t>
+  </si>
+  <si>
+    <t>one test for audio file is accpetable type</t>
+  </si>
+  <si>
+    <t>one test for playlist file is acceptable type</t>
+  </si>
+  <si>
+    <t>test for extract walk valid/invalide pattern</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -984,7 +959,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1025,264 +1000,196 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="45">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1341,47 +1248,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1389,12 +1312,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1421,7 +1344,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1442,7 +1365,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1493,7 +1416,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1509,32 +1432,31 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45.71"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="63" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1550,8 +1472,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1574,7 +1496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -1595,7 +1517,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
@@ -1618,7 +1540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -1641,7 +1563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1662,7 +1584,7 @@
       </c>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1683,7 +1605,7 @@
       </c>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -1706,7 +1628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
@@ -1729,7 +1651,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
@@ -1752,7 +1674,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
@@ -1773,7 +1695,7 @@
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
@@ -1794,7 +1716,7 @@
       </c>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
@@ -1815,7 +1737,7 @@
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>47</v>
       </c>
@@ -1836,7 +1758,7 @@
       </c>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>50</v>
       </c>
@@ -1857,7 +1779,7 @@
       </c>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
@@ -1880,7 +1802,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
@@ -1901,7 +1823,7 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
@@ -1922,7 +1844,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
@@ -1943,7 +1865,7 @@
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>63</v>
       </c>
@@ -1964,7 +1886,7 @@
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>68</v>
       </c>
@@ -1985,41 +1907,33 @@
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="33.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="76.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="79.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="4" width="8.57"/>
+    <col min="1" max="1" width="22.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="39" style="4" customWidth="1"/>
+    <col min="6" max="6" width="76.7109375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="79.140625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2027,7 +1941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -2035,7 +1949,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +1972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -2079,7 +1993,7 @@
       </c>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>73</v>
       </c>
@@ -2100,7 +2014,7 @@
       </c>
       <c r="G6" s="17"/>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>77</v>
       </c>
@@ -2123,7 +2037,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>77</v>
       </c>
@@ -2144,7 +2058,7 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>77</v>
       </c>
@@ -2165,7 +2079,7 @@
       </c>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>88</v>
       </c>
@@ -2188,7 +2102,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>88</v>
       </c>
@@ -2211,7 +2125,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>88</v>
       </c>
@@ -2232,7 +2146,7 @@
       </c>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>99</v>
       </c>
@@ -2255,7 +2169,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>104</v>
       </c>
@@ -2278,7 +2192,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>104</v>
       </c>
@@ -2301,7 +2215,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>112</v>
       </c>
@@ -2324,7 +2238,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>112</v>
       </c>
@@ -2347,7 +2261,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>119</v>
       </c>
@@ -2366,7 +2280,7 @@
       <c r="F18" s="14"/>
       <c r="G18" s="17"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>119</v>
       </c>
@@ -2387,7 +2301,7 @@
       </c>
       <c r="G19" s="21"/>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>119</v>
       </c>
@@ -2410,7 +2324,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>126</v>
       </c>
@@ -2431,7 +2345,7 @@
       </c>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>126</v>
       </c>
@@ -2454,7 +2368,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>126</v>
       </c>
@@ -2475,7 +2389,7 @@
       </c>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>134</v>
       </c>
@@ -2498,7 +2412,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>134</v>
       </c>
@@ -2519,7 +2433,7 @@
       </c>
       <c r="G25" s="17"/>
     </row>
-    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>140</v>
       </c>
@@ -2542,7 +2456,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>140</v>
       </c>
@@ -2565,7 +2479,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>140</v>
       </c>
@@ -2588,7 +2502,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>152</v>
       </c>
@@ -2611,7 +2525,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>156</v>
       </c>
@@ -2634,7 +2548,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>156</v>
       </c>
@@ -2655,7 +2569,7 @@
       </c>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>156</v>
       </c>
@@ -2676,7 +2590,7 @@
       </c>
       <c r="G32" s="13"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>166</v>
       </c>
@@ -2699,7 +2613,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>166</v>
       </c>
@@ -2720,7 +2634,7 @@
       </c>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>166</v>
       </c>
@@ -2741,7 +2655,7 @@
       </c>
       <c r="G35" s="16"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>172</v>
       </c>
@@ -2762,7 +2676,7 @@
       </c>
       <c r="G36" s="25"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>175</v>
       </c>
@@ -2783,7 +2697,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>178</v>
       </c>
@@ -2805,35 +2719,27 @@
       <c r="G38" s="25"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="26" width="69.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="26.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="58.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="31.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="27" width="8.57"/>
+    <col min="1" max="1" width="18.5703125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="69.28515625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="58.140625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" style="26" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -2841,7 +2747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
@@ -2849,8 +2755,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2873,7 +2779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>11</v>
       </c>
@@ -2894,7 +2800,7 @@
       </c>
       <c r="G5" s="28"/>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>182</v>
       </c>
@@ -2915,7 +2821,7 @@
       </c>
       <c r="G6" s="29"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>182</v>
       </c>
@@ -2936,7 +2842,7 @@
       </c>
       <c r="G7" s="29"/>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
         <v>182</v>
       </c>
@@ -2957,7 +2863,7 @@
       </c>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>182</v>
       </c>
@@ -2978,7 +2884,7 @@
       </c>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
         <v>195</v>
       </c>
@@ -2999,7 +2905,7 @@
       </c>
       <c r="G10" s="32"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
         <v>195</v>
       </c>
@@ -3020,7 +2926,7 @@
       </c>
       <c r="G11" s="32"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
         <v>202</v>
       </c>
@@ -3044,34 +2950,26 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="37.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="85"/>
+    <col min="1" max="1" width="26.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="85" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3079,7 +2977,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -3087,8 +2985,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3111,7 +3009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -3132,7 +3030,7 @@
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>206</v>
       </c>
@@ -3140,7 +3038,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>100</v>
@@ -3155,7 +3053,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>206</v>
       </c>
@@ -3163,7 +3061,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>108</v>
@@ -3178,7 +3076,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>206</v>
       </c>
@@ -3186,7 +3084,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>108</v>
@@ -3201,7 +3099,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>213</v>
       </c>
@@ -3222,7 +3120,7 @@
       </c>
       <c r="G9" s="36"/>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>213</v>
       </c>
@@ -3243,7 +3141,7 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>219</v>
       </c>
@@ -3264,7 +3162,7 @@
       </c>
       <c r="G11" s="34"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>219</v>
       </c>
@@ -3285,7 +3183,7 @@
       </c>
       <c r="G12" s="34"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>219</v>
       </c>
@@ -3308,7 +3206,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
         <v>226</v>
       </c>
@@ -3329,7 +3227,7 @@
       </c>
       <c r="G14" s="36"/>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>226</v>
       </c>
@@ -3350,7 +3248,7 @@
       </c>
       <c r="G15" s="36"/>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>226</v>
       </c>
@@ -3373,7 +3271,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>230</v>
       </c>
@@ -3394,7 +3292,7 @@
       </c>
       <c r="G17" s="34"/>
     </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>230</v>
       </c>
@@ -3417,7 +3315,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>234</v>
       </c>
@@ -3425,7 +3323,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>235</v>
@@ -3440,7 +3338,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>234</v>
       </c>
@@ -3448,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>239</v>
@@ -3463,7 +3361,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>234</v>
       </c>
@@ -3471,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
         <v>242</v>
@@ -3486,7 +3384,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>245</v>
       </c>
@@ -3507,7 +3405,7 @@
       </c>
       <c r="G22" s="34"/>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
         <v>245</v>
       </c>
@@ -3515,151 +3413,120 @@
         <v>19</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D23" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="G24" s="36"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E25" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="36"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="G23" s="34" t="s">
+      <c r="E26" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" s="36" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="G24" s="34"/>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>44</v>
-      </c>
       <c r="G26" s="36"/>
     </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="G27" s="36"/>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="67.43"/>
+    <col min="1" max="1" width="21.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="46.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="67.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3682,7 +3549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
         <v>11</v>
       </c>
@@ -3703,9 +3570,9 @@
       </c>
       <c r="G5" s="37"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -3714,9 +3581,9 @@
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
@@ -3724,12 +3591,12 @@
       <c r="E7" s="33"/>
       <c r="F7" s="33"/>
       <c r="G7" s="33" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -3737,23 +3604,23 @@
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -3762,51 +3629,51 @@
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -3815,31 +3682,31 @@
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -3848,51 +3715,51 @@
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="G17" s="41"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="B17" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="43" t="s">
+      <c r="E18" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="F18" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="G18" s="41"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>282</v>
-      </c>
-      <c r="G17" s="43"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>283</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>284</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="G18" s="43"/>
-    </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="s">
-        <v>286</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -3901,20 +3768,20 @@
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>13</v>
@@ -3932,55 +3799,47 @@
         <v>13</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="79.57"/>
+    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="79.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -4003,7 +3862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -4024,176 +3883,163 @@
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" s="44" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
+    <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>296</v>
-      </c>
       <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="42" t="s">
         <v>207</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F7" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>298</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="39.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.29"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="43" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47" t="s">
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E9792C-919B-4A5C-8A2A-F3B1E70CCABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEABB477-7A55-4A99-8C0A-D1C5E1FB8F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="350">
   <si>
     <t>package</t>
   </si>
@@ -813,9 +813,6 @@
     <t>create_csv</t>
   </si>
   <si>
-    <t>mock the created file</t>
-  </si>
-  <si>
     <t>create_txt</t>
   </si>
   <si>
@@ -846,12 +843,6 @@
     <t>audio file &lt;tld&gt;/&lt;artist&gt;/&lt;audio&gt;.&lt;ext&gt;</t>
   </si>
   <si>
-    <t>get_file_ext</t>
-  </si>
-  <si>
-    <t>make_album_dir</t>
-  </si>
-  <si>
     <t>make_dir</t>
   </si>
   <si>
@@ -885,12 +876,6 @@
     <t>remove_pattern</t>
   </si>
   <si>
-    <t>tld_path</t>
-  </si>
-  <si>
-    <t>remove getter/setter. Never been used.</t>
-  </si>
-  <si>
     <t>src</t>
   </si>
   <si>
@@ -931,13 +916,178 @@
   </si>
   <si>
     <t>test for extract walk valid/invalide pattern</t>
+  </si>
+  <si>
+    <t>test_create_csv_alt_dir_sorted</t>
+  </si>
+  <si>
+    <t>happy path creating a sorted csv file in alternate directory</t>
+  </si>
+  <si>
+    <t>data list</t>
+  </si>
+  <si>
+    <t>test_create_txt_alt_dir</t>
+  </si>
+  <si>
+    <t>creating a text file in alternate directory</t>
+  </si>
+  <si>
+    <t>files created in generated_files/csv_files tested many other places</t>
+  </si>
+  <si>
+    <t>files created in generated_files/result_files tested many other places</t>
+  </si>
+  <si>
+    <t>test_get_audio_file</t>
+  </si>
+  <si>
+    <t>generates a csv containing full path for all audio files</t>
+  </si>
+  <si>
+    <t>/tests/Music</t>
+  </si>
+  <si>
+    <t>test_get_ext_file_list_all</t>
+  </si>
+  <si>
+    <t>/tests/Music, no pattern</t>
+  </si>
+  <si>
+    <t>/tests/Music, m4a</t>
+  </si>
+  <si>
+    <t>/tests/Music, mp3</t>
+  </si>
+  <si>
+    <t>/tests/Music, wma</t>
+  </si>
+  <si>
+    <t>generates a csv containing full file path for all valid extensions</t>
+  </si>
+  <si>
+    <t>generates a csv containing full file path for m4a</t>
+  </si>
+  <si>
+    <t>generates a csv containing full file path for mp3</t>
+  </si>
+  <si>
+    <t>generates a csv containing full file path for wma</t>
+  </si>
+  <si>
+    <t>test_get_ext_file_list_m4a</t>
+  </si>
+  <si>
+    <t>test_get_ext_file_list_mp3</t>
+  </si>
+  <si>
+    <t>test_get_ext_file_list_wma</t>
+  </si>
+  <si>
+    <t>test_make_dir</t>
+  </si>
+  <si>
+    <t>fail path ExecError</t>
+  </si>
+  <si>
+    <t>haqppy path</t>
+  </si>
+  <si>
+    <t>happy path Creates a directory</t>
+  </si>
+  <si>
+    <t>test_make_dir_fail</t>
+  </si>
+  <si>
+    <t>mock OSError?</t>
+  </si>
+  <si>
+    <t>test_move_audio_file</t>
+  </si>
+  <si>
+    <t>test_remove_pattern</t>
+  </si>
+  <si>
+    <t>test_move_audio_file_fail</t>
+  </si>
+  <si>
+    <t>test_remove_pattern_fail</t>
+  </si>
+  <si>
+    <t>test_remove_album_dir_permission</t>
+  </si>
+  <si>
+    <t>test_remove_album_dir</t>
+  </si>
+  <si>
+    <t>test_remove_pattern_permission</t>
+  </si>
+  <si>
+    <t>fail path OS persmission error while creating a directory</t>
+  </si>
+  <si>
+    <t>test_make_dir_permision</t>
+  </si>
+  <si>
+    <t>fail path general OS error while creating a directory</t>
+  </si>
+  <si>
+    <t>mock OSError with errno == EACCES</t>
+  </si>
+  <si>
+    <t>Fail pathgeneral  OSError</t>
+  </si>
+  <si>
+    <t>Fail path permission denied OSError</t>
+  </si>
+  <si>
+    <t>test_remove_album_dir_fail</t>
+  </si>
+  <si>
+    <t>fail path general OSError</t>
+  </si>
+  <si>
+    <t>fail path permission deined OSError</t>
+  </si>
+  <si>
+    <t>mock OSError with errno == EACCES?</t>
+  </si>
+  <si>
+    <t>a file from /tests/Music</t>
+  </si>
+  <si>
+    <t>non-extant file? Mock ExecError?</t>
+  </si>
+  <si>
+    <t>create temp /tests/tld/artist/album</t>
+  </si>
+  <si>
+    <t>delete  temp /tests/tld/ (recursive too) in teardown</t>
+  </si>
+  <si>
+    <t>non-extant dir? Mock osError?</t>
+  </si>
+  <si>
+    <t>non-extant pattern? Mock osError?</t>
+  </si>
+  <si>
+    <t>fake dir name, create in generated_files/Music</t>
+  </si>
+  <si>
+    <t>teardown cleans up generated_files/Music</t>
+  </si>
+  <si>
+    <t>movce 1 m4a/mp3/wma to a created temp dir</t>
+  </si>
+  <si>
+    <t>"?bad_path"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -965,6 +1115,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1054,7 +1210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1162,21 +1318,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1184,6 +1325,45 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1563,7 +1743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1574,17 +1754,19 @@
         <v>19</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1595,13 +1777,13 @@
         <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G9" s="6"/>
     </row>
@@ -1616,17 +1798,15 @@
         <v>19</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -1639,16 +1819,16 @@
         <v>19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3497,309 +3677,577 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="67.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="42" customWidth="1"/>
+    <col min="4" max="4" width="55.85546875" style="42" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" style="42" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="42" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="42" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="43" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="37"/>
+      <c r="G5" s="44"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" spans="1:7" s="42" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33" t="s">
+      <c r="B7" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>299</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="G9" s="47"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
         <v>262</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="G10" s="45"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="45"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="G12" s="45"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="G13" s="45"/>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
         <v>263</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="E14" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F14" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G14" s="47"/>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="E15" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F15" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G15" s="47"/>
+    </row>
+    <row r="16" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="B16" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="G17" s="49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="48" t="s">
+        <v>270</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="50" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="B19" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="B21" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
+      <c r="E21" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="F21" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E22" s="49" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F22" s="49" t="s">
         <v>278</v>
       </c>
-      <c r="G17" s="41"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="41" t="s">
+      <c r="G22" s="49"/>
+    </row>
+    <row r="23" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="B23" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
         <v>280</v>
       </c>
-      <c r="F18" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="G18" s="41"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>285</v>
+      <c r="B26" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F26" s="49" t="s">
+        <v>348</v>
+      </c>
+      <c r="G26" s="49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>326</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="G28" s="49" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3827,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3835,7 +4283,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3885,7 +4333,7 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>19</v>
@@ -3897,36 +4345,36 @@
         <v>108</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="37" t="s">
         <v>207</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3961,82 +4409,82 @@
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="38" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEABB477-7A55-4A99-8C0A-D1C5E1FB8F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1B0631-6963-478F-9640-53C0B222A073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="344">
   <si>
     <t>package</t>
   </si>
@@ -846,9 +846,6 @@
     <t>make_dir</t>
   </si>
   <si>
-    <t>move_audio_file</t>
-  </si>
-  <si>
     <t>path_info</t>
   </si>
   <si>
@@ -987,9 +984,6 @@
     <t>test_make_dir</t>
   </si>
   <si>
-    <t>fail path ExecError</t>
-  </si>
-  <si>
     <t>haqppy path</t>
   </si>
   <si>
@@ -1002,15 +996,9 @@
     <t>mock OSError?</t>
   </si>
   <si>
-    <t>test_move_audio_file</t>
-  </si>
-  <si>
     <t>test_remove_pattern</t>
   </si>
   <si>
-    <t>test_move_audio_file_fail</t>
-  </si>
-  <si>
     <t>test_remove_pattern_fail</t>
   </si>
   <si>
@@ -1051,12 +1039,6 @@
   </si>
   <si>
     <t>mock OSError with errno == EACCES?</t>
-  </si>
-  <si>
-    <t>a file from /tests/Music</t>
-  </si>
-  <si>
-    <t>non-extant file? Mock ExecError?</t>
   </si>
   <si>
     <t>create temp /tests/tld/artist/album</t>
@@ -3677,7 +3659,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="42" bestFit="1" customWidth="1"/>
@@ -3773,16 +3755,16 @@
         <v>19</v>
       </c>
       <c r="D7" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>297</v>
-      </c>
       <c r="G7" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3796,16 +3778,16 @@
         <v>19</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3819,13 +3801,13 @@
         <v>19</v>
       </c>
       <c r="D9" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="47" t="s">
         <v>303</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>304</v>
       </c>
       <c r="G9" s="47"/>
     </row>
@@ -3840,13 +3822,13 @@
         <v>19</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="F10" s="45" t="s">
         <v>305</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>306</v>
       </c>
       <c r="G10" s="45"/>
     </row>
@@ -3861,13 +3843,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G11" s="45"/>
     </row>
@@ -3882,13 +3864,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G12" s="45"/>
     </row>
@@ -3903,13 +3885,13 @@
         <v>19</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G13" s="45"/>
     </row>
@@ -3966,16 +3948,16 @@
         <v>19</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3989,16 +3971,16 @@
         <v>207</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4012,19 +3994,19 @@
         <v>207</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F18" s="49" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
         <v>271</v>
       </c>
@@ -4032,22 +4014,20 @@
         <v>19</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="G19" s="51"/>
+    </row>
+    <row r="20" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
         <v>271</v>
       </c>
@@ -4055,84 +4035,86 @@
         <v>19</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="G20" s="51" t="s">
-        <v>347</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="G20" s="51"/>
     </row>
     <row r="21" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="E21" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="G21" s="49"/>
+        <v>278</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="22" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>277</v>
-      </c>
-      <c r="F22" s="49" t="s">
         <v>278</v>
       </c>
-      <c r="G22" s="49"/>
+      <c r="B22" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>332</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>338</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="23" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="51" t="s">
+      <c r="A23" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="D23" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>343</v>
+      <c r="D23" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>323</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>335</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
@@ -4146,16 +4128,16 @@
         <v>207</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>334</v>
+        <v>100</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
@@ -4169,85 +4151,39 @@
         <v>207</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F25" s="51" t="s">
         <v>339</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="49" t="s">
+      <c r="A26" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>348</v>
-      </c>
-      <c r="G26" s="49" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
-        <v>280</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>337</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>326</v>
-      </c>
-      <c r="F27" s="49" t="s">
-        <v>345</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="48" t="s">
-        <v>280</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="E28" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F28" s="49" t="s">
-        <v>339</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>339</v>
+      <c r="D26" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4283,7 +4219,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4333,7 +4269,7 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>19</v>
@@ -4345,18 +4281,18 @@
         <v>108</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>285</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>19</v>
@@ -4368,13 +4304,13 @@
         <v>108</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>288</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -4436,7 +4372,7 @@
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
       <c r="D5" s="39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
@@ -4447,7 +4383,7 @@
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -4458,7 +4394,7 @@
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
       <c r="D7" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
@@ -4469,7 +4405,7 @@
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
@@ -4480,7 +4416,7 @@
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
       <c r="D9" s="39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1B0631-6963-478F-9640-53C0B222A073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB17C4A-7F95-4D59-BF08-7A3A7D86836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="353">
   <si>
     <t>package</t>
   </si>
@@ -342,9 +342,6 @@
     <t>select audio file from test/Music, move to  testSetup built PreppedMusic</t>
   </si>
   <si>
-    <t>calls get_media_tags, make_album_dir, move_audio_file, create_csv. Test support functions seperately.</t>
-  </si>
-  <si>
     <t>get_any_tags</t>
   </si>
   <si>
@@ -1063,6 +1060,36 @@
   </si>
   <si>
     <t>"?bad_path"</t>
+  </si>
+  <si>
+    <t>fail path on ExecError</t>
+  </si>
+  <si>
+    <t>fail path on ValidationError</t>
+  </si>
+  <si>
+    <t>test_create_album_dir_exec</t>
+  </si>
+  <si>
+    <t>test_create_album_dir_validate</t>
+  </si>
+  <si>
+    <t>mock pathvalidate?</t>
+  </si>
+  <si>
+    <t>mock shutil?</t>
+  </si>
+  <si>
+    <t>calls get_media_tags, make_album_dir, create_csv. Test support functions seperately.</t>
+  </si>
+  <si>
+    <t>callget_media_tags, make_album_dir, create_csv. Test support functions moperately.</t>
+  </si>
+  <si>
+    <t>callget_media_tags, make_media_info_walk, get_csv. Test support functions a perately.</t>
+  </si>
+  <si>
+    <t>callget_media_tags, make_media_tags, get_csv. Test support functions auperately.</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="8" customWidth="1"/>
@@ -2308,7 +2335,7 @@
       </c>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>99</v>
       </c>
@@ -2328,540 +2355,540 @@
         <v>102</v>
       </c>
       <c r="G13" s="13" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="B16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="F16" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="E18" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="E19" s="12" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G19" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="17"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="20" t="s">
+      <c r="E20" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E22" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>131</v>
+      <c r="G22" s="21" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="F23" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="13"/>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="G23" s="24"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="B26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G26" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="17" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="15" t="s">
+      <c r="F27" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="G27" s="17"/>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G25" s="17"/>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="B28" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="23" t="s">
+      <c r="E28" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="F28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="G28" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="G26" s="25" t="s">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="23" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="23" t="s">
+      <c r="E29" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="F29" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="G29" s="13" t="s">
         <v>147</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>158</v>
+        <v>139</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>149</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G31" s="13"/>
+      <c r="A31" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="E32" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="G32" s="13"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" s="17"/>
+      <c r="G34" s="13"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="F35" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="G35" s="16"/>
+        <v>135</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="G36" s="25"/>
+      <c r="A36" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="17"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>176</v>
+      <c r="D37" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>169</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G37" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>19</v>
@@ -2873,12 +2900,54 @@
         <v>100</v>
       </c>
       <c r="E38" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" s="17"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="G38" s="25"/>
+      <c r="G40" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2914,7 +2983,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2964,28 +3033,28 @@
     </row>
     <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="30" t="s">
+      <c r="E6" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="F6" s="30" t="s">
         <v>184</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>185</v>
       </c>
       <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>19</v>
@@ -2994,19 +3063,19 @@
         <v>19</v>
       </c>
       <c r="D7" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="F7" s="30" t="s">
         <v>187</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>188</v>
       </c>
       <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>19</v>
@@ -3015,19 +3084,19 @@
         <v>19</v>
       </c>
       <c r="D8" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="F8" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>191</v>
       </c>
       <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>19</v>
@@ -3036,40 +3105,40 @@
         <v>19</v>
       </c>
       <c r="D9" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="30" t="s">
         <v>193</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>194</v>
       </c>
       <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="32" t="s">
+      <c r="E10" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="F10" s="32" t="s">
         <v>197</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>198</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>19</v>
@@ -3078,19 +3147,19 @@
         <v>19</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="F11" s="32" t="s">
         <v>200</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>201</v>
       </c>
       <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B12" s="29" t="s">
         <v>12</v>
@@ -3108,7 +3177,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3136,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3144,7 +3213,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3194,7 +3263,7 @@
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>19</v>
@@ -3206,18 +3275,18 @@
         <v>100</v>
       </c>
       <c r="E6" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="G6" s="34" t="s">
         <v>209</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>19</v>
@@ -3226,21 +3295,21 @@
         <v>19</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F7" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>209</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>19</v>
@@ -3249,42 +3318,42 @@
         <v>19</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F8" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>209</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="36" t="s">
+      <c r="E9" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="F9" s="36" t="s">
         <v>215</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>216</v>
       </c>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>19</v>
@@ -3293,10 +3362,10 @@
         <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" s="36" t="s">
         <v>217</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>218</v>
       </c>
       <c r="F10" s="36" t="s">
         <v>44</v>
@@ -3305,7 +3374,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>19</v>
@@ -3317,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>44</v>
@@ -3326,7 +3395,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>19</v>
@@ -3335,19 +3404,19 @@
         <v>19</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" s="34" t="s">
         <v>221</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>222</v>
       </c>
       <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>19</v>
@@ -3356,21 +3425,21 @@
         <v>19</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="G13" s="34" t="s">
         <v>224</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>19</v>
@@ -3382,16 +3451,16 @@
         <v>100</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B15" s="36" t="s">
         <v>19</v>
@@ -3400,19 +3469,19 @@
         <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="36" t="s">
         <v>19</v>
@@ -3421,21 +3490,21 @@
         <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F16" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" s="36" t="s">
         <v>224</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>19</v>
@@ -3447,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F17" s="34" t="s">
         <v>44</v>
@@ -3456,7 +3525,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>19</v>
@@ -3465,44 +3534,44 @@
         <v>19</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F18" s="34" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="36" t="s">
+      <c r="E19" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="F19" s="36" t="s">
         <v>236</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="G19" s="36" t="s">
         <v>237</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>19</v>
@@ -3511,21 +3580,21 @@
         <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="F20" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="G20" s="36" t="s">
         <v>240</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" s="36" t="s">
         <v>19</v>
@@ -3534,21 +3603,21 @@
         <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="F21" s="36" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="36" t="s">
-        <v>244</v>
-      </c>
       <c r="G21" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>19</v>
@@ -3560,7 +3629,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>44</v>
@@ -3569,7 +3638,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>19</v>
@@ -3578,19 +3647,19 @@
         <v>19</v>
       </c>
       <c r="D23" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>249</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>250</v>
       </c>
       <c r="G23" s="34"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" s="36" t="s">
         <v>19</v>
@@ -3602,16 +3671,16 @@
         <v>100</v>
       </c>
       <c r="E24" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="F24" s="36" t="s">
         <v>252</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>253</v>
       </c>
       <c r="G24" s="36"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B25" s="36" t="s">
         <v>19</v>
@@ -3620,10 +3689,10 @@
         <v>19</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F25" s="36" t="s">
         <v>44</v>
@@ -3632,7 +3701,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B26" s="36" t="s">
         <v>19</v>
@@ -3641,13 +3710,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G26" s="36"/>
     </row>
@@ -3677,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3685,7 +3754,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3735,7 +3804,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45"/>
@@ -3746,7 +3815,7 @@
     </row>
     <row r="7" spans="1:7" s="42" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B7" s="41" t="s">
         <v>19</v>
@@ -3755,21 +3824,21 @@
         <v>19</v>
       </c>
       <c r="D7" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>296</v>
-      </c>
       <c r="G7" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B8" s="45" t="s">
         <v>19</v>
@@ -3778,21 +3847,21 @@
         <v>19</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>19</v>
@@ -3801,19 +3870,19 @@
         <v>19</v>
       </c>
       <c r="D9" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" s="47" t="s">
         <v>302</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>303</v>
       </c>
       <c r="G9" s="47"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B10" s="45" t="s">
         <v>19</v>
@@ -3822,19 +3891,19 @@
         <v>19</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E10" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" s="45" t="s">
         <v>304</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>305</v>
       </c>
       <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>19</v>
@@ -3843,19 +3912,19 @@
         <v>19</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G11" s="45"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>19</v>
@@ -3864,19 +3933,19 @@
         <v>19</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>19</v>
@@ -3885,40 +3954,40 @@
         <v>19</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G13" s="45"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>263</v>
       </c>
-      <c r="B14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="47" t="s">
+      <c r="E14" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="F14" s="47" t="s">
         <v>265</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>266</v>
       </c>
       <c r="G14" s="47"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>19</v>
@@ -3927,19 +3996,19 @@
         <v>19</v>
       </c>
       <c r="D15" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="F15" s="47" t="s">
         <v>268</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>269</v>
       </c>
       <c r="G15" s="47"/>
     </row>
     <row r="16" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B16" s="49" t="s">
         <v>19</v>
@@ -3948,88 +4017,88 @@
         <v>19</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F16" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="G16" s="49" t="s">
         <v>340</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B17" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B18" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D18" s="49" t="s">
+        <v>325</v>
+      </c>
+      <c r="E18" s="49" t="s">
         <v>326</v>
       </c>
-      <c r="E18" s="49" t="s">
-        <v>327</v>
-      </c>
       <c r="F18" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="51" t="s">
         <v>271</v>
       </c>
-      <c r="B19" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="51" t="s">
+      <c r="E19" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="F19" s="51" t="s">
         <v>273</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>274</v>
       </c>
       <c r="G19" s="51"/>
     </row>
     <row r="20" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>19</v>
@@ -4038,152 +4107,152 @@
         <v>19</v>
       </c>
       <c r="D20" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="F20" s="51" t="s">
         <v>276</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>277</v>
       </c>
       <c r="G20" s="51"/>
     </row>
     <row r="21" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B21" s="48" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F21" s="48" t="s">
+        <v>335</v>
+      </c>
+      <c r="G21" s="48" t="s">
         <v>336</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B22" s="48" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G22" s="48" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B23" s="48" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G23" s="48" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D24" s="51" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D26" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="F26" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="E26" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>335</v>
-      </c>
       <c r="G26" s="51" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4211,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4219,7 +4288,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4269,48 +4338,48 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="F6" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>284</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" s="12" t="s">
+      <c r="F7" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4372,7 +4441,7 @@
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
       <c r="D5" s="39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
@@ -4383,7 +4452,7 @@
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -4394,7 +4463,7 @@
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
       <c r="D7" s="39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
@@ -4405,7 +4474,7 @@
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
@@ -4416,7 +4485,7 @@
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
       <c r="D9" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB17C4A-7F95-4D59-BF08-7A3A7D86836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECB5543-B115-4BAB-9FC8-E69CEC571CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="350">
   <si>
     <t>package</t>
   </si>
@@ -1074,22 +1074,13 @@
     <t>test_create_album_dir_validate</t>
   </si>
   <si>
-    <t>mock pathvalidate?</t>
-  </si>
-  <si>
-    <t>mock shutil?</t>
-  </si>
-  <si>
     <t>calls get_media_tags, make_album_dir, create_csv. Test support functions seperately.</t>
   </si>
   <si>
-    <t>callget_media_tags, make_album_dir, create_csv. Test support functions moperately.</t>
-  </si>
-  <si>
-    <t>callget_media_tags, make_media_info_walk, get_csv. Test support functions a perately.</t>
-  </si>
-  <si>
-    <t>callget_media_tags, make_media_tags, get_csv. Test support functions auperately.</t>
+    <t>mock ExecError</t>
+  </si>
+  <si>
+    <t>mock ValueError</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1364,14 +1355,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2355,7 +2340,7 @@
         <v>102</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2396,7 +2381,7 @@
         <v>346</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G15" s="13"/>
     </row>
@@ -3836,7 +3821,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
         <v>259</v>
       </c>
@@ -4006,7 +3991,7 @@
       </c>
       <c r="G15" s="47"/>
     </row>
-    <row r="16" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
         <v>269</v>
       </c>
@@ -4029,7 +4014,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
         <v>269</v>
       </c>
@@ -4037,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>327</v>
@@ -4052,7 +4037,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
         <v>269</v>
       </c>
@@ -4060,7 +4045,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>325</v>
@@ -4075,49 +4060,49 @@
         <v>340</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="B19" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="51" t="s">
+      <c r="B19" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="G19" s="51"/>
-    </row>
-    <row r="20" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="47"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="51" t="s">
+      <c r="B20" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="G20" s="51"/>
-    </row>
-    <row r="21" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G20" s="47"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>277</v>
       </c>
@@ -4125,7 +4110,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>316</v>
@@ -4140,7 +4125,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
         <v>277</v>
       </c>
@@ -4163,7 +4148,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="48" t="s">
         <v>277</v>
       </c>
@@ -4186,72 +4171,72 @@
         <v>336</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="B24" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="51" t="s">
+      <c r="B24" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="51" t="s">
+      <c r="E24" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="F24" s="51" t="s">
+      <c r="F24" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G24" s="47" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="B25" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="51" t="s">
+      <c r="B25" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="47" t="s">
         <v>338</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="47" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="B26" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="51" t="s">
+      <c r="B26" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="47" t="s">
         <v>333</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="47" t="s">
         <v>324</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="47" t="s">
         <v>334</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="47" t="s">
         <v>334</v>
       </c>
     </row>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECB5543-B115-4BAB-9FC8-E69CEC571CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E559CE55-8CC7-4A9F-BB0C-43BAB6719D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="371">
   <si>
     <t>package</t>
   </si>
@@ -879,24 +879,12 @@
     <t>popen_pipe</t>
   </si>
   <si>
-    <t>test_subprocess_popen_pipe_invalid_file</t>
-  </si>
-  <si>
     <t>m3u file</t>
   </si>
   <si>
-    <t>this is really a SubprocessUtilities.popen_pipe test, adapt for test_subprocess_utilities</t>
-  </si>
-  <si>
     <t>subprocess_run</t>
   </si>
   <si>
-    <t>test_subprocess_run_invalid_file</t>
-  </si>
-  <si>
-    <t>this is really a SubprocessUtilities.subprocess_run test, adapt for test_subprocess_utilities</t>
-  </si>
-  <si>
     <t>one test for file existance</t>
   </si>
   <si>
@@ -990,9 +978,6 @@
     <t>test_make_dir_fail</t>
   </si>
   <si>
-    <t>mock OSError?</t>
-  </si>
-  <si>
     <t>test_remove_pattern</t>
   </si>
   <si>
@@ -1035,21 +1020,12 @@
     <t>fail path permission deined OSError</t>
   </si>
   <si>
-    <t>mock OSError with errno == EACCES?</t>
-  </si>
-  <si>
     <t>create temp /tests/tld/artist/album</t>
   </si>
   <si>
     <t>delete  temp /tests/tld/ (recursive too) in teardown</t>
   </si>
   <si>
-    <t>non-extant dir? Mock osError?</t>
-  </si>
-  <si>
-    <t>non-extant pattern? Mock osError?</t>
-  </si>
-  <si>
     <t>fake dir name, create in generated_files/Music</t>
   </si>
   <si>
@@ -1081,6 +1057,93 @@
   </si>
   <si>
     <t>mock ValueError</t>
+  </si>
+  <si>
+    <t>fail path trying to removes files from a mount point</t>
+  </si>
+  <si>
+    <t>test_remove_pattern_mount</t>
+  </si>
+  <si>
+    <t>mock MusicProcessingError</t>
+  </si>
+  <si>
+    <t>Mock osError</t>
+  </si>
+  <si>
+    <t>fail path trying to removes files from a file system root</t>
+  </si>
+  <si>
+    <t>test_remove_pattern_root</t>
+  </si>
+  <si>
+    <t>fail path trying to removes files with *.* wildcard</t>
+  </si>
+  <si>
+    <t>test_remove_pattern_wildcard</t>
+  </si>
+  <si>
+    <t>pattern = *.*</t>
+  </si>
+  <si>
+    <t>test_popen_pipe_ffmpeg_invalid_file</t>
+  </si>
+  <si>
+    <t>fail path, trying to get ffprobe media info from invalid file type</t>
+  </si>
+  <si>
+    <t>test_popen_pipe_ffmpegprocess_error</t>
+  </si>
+  <si>
+    <t>mocking</t>
+  </si>
+  <si>
+    <t>test_popen_pipe_ffprobe_invalid_file</t>
+  </si>
+  <si>
+    <t>ffmpeg command</t>
+  </si>
+  <si>
+    <t>ffprobe command</t>
+  </si>
+  <si>
+    <t>ffmpeg command throws FfmpegProcessError (non-zero popen pipe ret code)</t>
+  </si>
+  <si>
+    <t>fail path ffprobe media info from invalid file type throws RuntimeError</t>
+  </si>
+  <si>
+    <t>fail path ffprobe command throws UnicodeDecodeError</t>
+  </si>
+  <si>
+    <t>test_popen_pipe_unicode_error</t>
+  </si>
+  <si>
+    <t>fail path, nvalid file type throws CalledProcessError</t>
+  </si>
+  <si>
+    <t>test_subprocess_run_ffmpeg_invalid_file</t>
+  </si>
+  <si>
+    <t>test_subprocess_run_ffprobe_non_extant</t>
+  </si>
+  <si>
+    <t>fail path, non-extant file throws CalledProcessError</t>
+  </si>
+  <si>
+    <t>non extant wave file</t>
+  </si>
+  <si>
+    <t>fail path, command throws UnicodeDecodeError</t>
+  </si>
+  <si>
+    <t>ffprobe or ffmpeg command</t>
+  </si>
+  <si>
+    <t>test_subprocess_run_unicode_error</t>
+  </si>
+  <si>
+    <t>fail path, command  throws FfmpegProcessError</t>
   </si>
 </sst>
 </file>
@@ -1109,18 +1172,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1210,7 +1270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1318,45 +1378,61 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2340,7 +2416,7 @@
         <v>102</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2354,13 +2430,13 @@
         <v>206</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G14" s="13"/>
     </row>
@@ -2375,13 +2451,13 @@
         <v>206</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G15" s="13"/>
     </row>
@@ -3713,532 +3789,591 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="42" customWidth="1"/>
-    <col min="4" max="4" width="55.85546875" style="42" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" style="42" customWidth="1"/>
-    <col min="6" max="6" width="44.5703125" style="42" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.5703125" style="40"/>
+    <col min="1" max="1" width="18.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="55.85546875" style="41" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" style="41" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" style="41" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="44"/>
+      <c r="G5" s="43"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" spans="1:7" s="42" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" spans="1:7" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="41" t="s">
+      <c r="B7" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="40" t="s">
         <v>294</v>
       </c>
-      <c r="E7" s="42" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="E8" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="G8" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="41" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="46" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>295</v>
-      </c>
-      <c r="G8" s="46" t="s">
+      <c r="G9" s="46"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="47" t="s">
+      <c r="F10" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="G10" s="44"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="F9" s="47" t="s">
+      <c r="G11" s="44"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F12" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="47"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="G12" s="44"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="E10" s="45" t="s">
+      <c r="B13" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="F10" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="G10" s="45"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="45" t="s">
+      <c r="G13" s="44"/>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" s="46"/>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="G15" s="46"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>334</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>323</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="G19" s="46"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" s="46"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="F11" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="G11" s="45"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>310</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>306</v>
-      </c>
-      <c r="G12" s="45"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>311</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>307</v>
-      </c>
-      <c r="G13" s="45"/>
-    </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" s="47"/>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>268</v>
-      </c>
-      <c r="G15" s="47"/>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="B16" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="49" t="s">
+      <c r="E21" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>326</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>345</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>325</v>
+      </c>
+      <c r="E23" s="47" t="s">
         <v>317</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="F23" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="F16" s="49" t="s">
-        <v>339</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="49" t="s">
+      <c r="F24" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="E17" s="49" t="s">
-        <v>318</v>
-      </c>
-      <c r="F17" s="49" t="s">
+      <c r="E25" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="G25" s="46"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="G26" s="46"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="G17" s="49" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="B18" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>325</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>326</v>
-      </c>
-      <c r="F18" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="G18" s="49" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="G19" s="47"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>274</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="G20" s="47"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>323</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>337</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>330</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>334</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="50" t="s">
+      <c r="E27" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="G27" s="46"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="49" t="s">
         <v>278</v>
       </c>
-      <c r="B24" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>341</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="50" t="s">
+      <c r="B28" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
         <v>278</v>
       </c>
-      <c r="B25" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>332</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>321</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>338</v>
-      </c>
-      <c r="G25" s="47" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>324</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>334</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>334</v>
-      </c>
+      <c r="B29" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="G29" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4248,123 +4383,239 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="79.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="65.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="50" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="12"/>
-    </row>
-    <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="G5" s="54"/>
+    </row>
+    <row r="6" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="55" t="s">
         <v>281</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="B6" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>352</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>351</v>
+      </c>
+      <c r="F6" s="55" t="s">
         <v>282</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="55" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>353</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>355</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>282</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>361</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="54" t="s">
         <v>283</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="37" t="s">
+      <c r="B10" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>365</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>287</v>
+      <c r="D12" s="54" t="s">
+        <v>367</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>369</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>354</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -4399,82 +4650,82 @@
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39" t="s">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-    </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E559CE55-8CC7-4A9F-BB0C-43BAB6719D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CD5CE6-BE7B-4AFB-BAAE-FD4C9133A8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="373">
   <si>
     <t>package</t>
   </si>
@@ -1144,6 +1144,12 @@
   </si>
   <si>
     <t>fail path, command  throws FfmpegProcessError</t>
+  </si>
+  <si>
+    <t>mock stdout</t>
+  </si>
+  <si>
+    <t>mock stdout or stderr</t>
   </si>
 </sst>
 </file>
@@ -4488,7 +4494,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>370</v>
@@ -4543,7 +4549,7 @@
         <v>361</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>357</v>
@@ -4612,7 +4618,7 @@
         <v>369</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="G12" s="54" t="s">
         <v>368</v>

--- a/excel_files/Testing.xlsx
+++ b/excel_files/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CD5CE6-BE7B-4AFB-BAAE-FD4C9133A8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5C7FB1-604B-4C0B-AC39-7B479E9DE94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AudioArt" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="372">
   <si>
     <t>package</t>
   </si>
@@ -651,9 +651,6 @@
     <t>__loudnorm_json_parse</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>test_loudnorm_json_parse</t>
   </si>
   <si>
@@ -1047,9 +1044,6 @@
     <t>test_create_album_dir_exec</t>
   </si>
   <si>
-    <t>test_create_album_dir_validate</t>
-  </si>
-  <si>
     <t>calls get_media_tags, make_album_dir, create_csv. Test support functions seperately.</t>
   </si>
   <si>
@@ -1095,9 +1089,6 @@
     <t>test_popen_pipe_ffmpegprocess_error</t>
   </si>
   <si>
-    <t>mocking</t>
-  </si>
-  <si>
     <t>test_popen_pipe_ffprobe_invalid_file</t>
   </si>
   <si>
@@ -1116,9 +1107,6 @@
     <t>fail path ffprobe command throws UnicodeDecodeError</t>
   </si>
   <si>
-    <t>test_popen_pipe_unicode_error</t>
-  </si>
-  <si>
     <t>fail path, nvalid file type throws CalledProcessError</t>
   </si>
   <si>
@@ -1140,16 +1128,25 @@
     <t>ffprobe or ffmpeg command</t>
   </si>
   <si>
-    <t>test_subprocess_run_unicode_error</t>
-  </si>
-  <si>
     <t>fail path, command  throws FfmpegProcessError</t>
   </si>
   <si>
-    <t>mock stdout</t>
-  </si>
-  <si>
-    <t>mock stdout or stderr</t>
+    <t>test_popen_pipe_communicate_decode_error</t>
+  </si>
+  <si>
+    <t>mock UnicodeDecodeError</t>
+  </si>
+  <si>
+    <t>mock subprocess.Popen().communicate()</t>
+  </si>
+  <si>
+    <t>m3u file, valid audio output file</t>
+  </si>
+  <si>
+    <t>test_subprocess_run_unicode_decode_error</t>
+  </si>
+  <si>
+    <t>test_create_album_dir_value</t>
   </si>
 </sst>
 </file>
@@ -2422,7 +2419,7 @@
         <v>102</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2433,16 +2430,16 @@
         <v>19</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G14" s="13"/>
     </row>
@@ -2454,16 +2451,16 @@
         <v>19</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G15" s="13"/>
     </row>
@@ -3342,13 +3339,13 @@
         <v>100</v>
       </c>
       <c r="E6" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="G6" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3365,13 +3362,13 @@
         <v>107</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F7" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3388,39 +3385,39 @@
         <v>107</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F8" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="36" t="s">
+      <c r="E9" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="F9" s="36" t="s">
         <v>214</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>215</v>
       </c>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>19</v>
@@ -3429,10 +3426,10 @@
         <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="36" t="s">
         <v>216</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>217</v>
       </c>
       <c r="F10" s="36" t="s">
         <v>44</v>
@@ -3441,7 +3438,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>19</v>
@@ -3453,7 +3450,7 @@
         <v>100</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>44</v>
@@ -3462,7 +3459,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>19</v>
@@ -3474,16 +3471,16 @@
         <v>107</v>
       </c>
       <c r="E12" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="34" t="s">
         <v>220</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>221</v>
       </c>
       <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>19</v>
@@ -3495,18 +3492,18 @@
         <v>107</v>
       </c>
       <c r="E13" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="G13" s="34" t="s">
         <v>223</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>19</v>
@@ -3518,16 +3515,16 @@
         <v>100</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B15" s="36" t="s">
         <v>19</v>
@@ -3539,16 +3536,16 @@
         <v>107</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B16" s="36" t="s">
         <v>19</v>
@@ -3560,18 +3557,18 @@
         <v>107</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F16" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="36" t="s">
         <v>223</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>19</v>
@@ -3583,7 +3580,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F17" s="34" t="s">
         <v>44</v>
@@ -3592,7 +3589,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>19</v>
@@ -3604,41 +3601,41 @@
         <v>107</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F18" s="34" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="36" t="s">
+      <c r="E19" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="F19" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="G19" s="36" t="s">
         <v>236</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>19</v>
@@ -3647,21 +3644,21 @@
         <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="F20" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" s="36" t="s">
         <v>239</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" s="36" t="s">
         <v>19</v>
@@ -3670,21 +3667,21 @@
         <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="F21" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="F21" s="36" t="s">
-        <v>243</v>
-      </c>
       <c r="G21" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>19</v>
@@ -3696,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>44</v>
@@ -3705,7 +3702,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>19</v>
@@ -3714,19 +3711,19 @@
         <v>19</v>
       </c>
       <c r="D23" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>248</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>249</v>
       </c>
       <c r="G23" s="34"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B24" s="36" t="s">
         <v>19</v>
@@ -3738,16 +3735,16 @@
         <v>100</v>
       </c>
       <c r="E24" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" s="36" t="s">
         <v>251</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>252</v>
       </c>
       <c r="G24" s="36"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" s="36" t="s">
         <v>19</v>
@@ -3756,10 +3753,10 @@
         <v>19</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F25" s="36" t="s">
         <v>44</v>
@@ -3768,7 +3765,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="36" t="s">
         <v>19</v>
@@ -3777,13 +3774,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G26" s="36"/>
     </row>
@@ -3813,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3821,7 +3818,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3871,7 +3868,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -3882,7 +3879,7 @@
     </row>
     <row r="7" spans="1:7" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B7" s="40" t="s">
         <v>19</v>
@@ -3891,21 +3888,21 @@
         <v>19</v>
       </c>
       <c r="D7" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="E7" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>291</v>
-      </c>
       <c r="G7" s="40" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>19</v>
@@ -3914,21 +3911,21 @@
         <v>19</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>19</v>
@@ -3937,19 +3934,19 @@
         <v>19</v>
       </c>
       <c r="D9" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="46" t="s">
         <v>297</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>298</v>
       </c>
       <c r="G9" s="46"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>19</v>
@@ -3958,19 +3955,19 @@
         <v>19</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E10" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>299</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>300</v>
       </c>
       <c r="G10" s="44"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B11" s="44" t="s">
         <v>19</v>
@@ -3979,19 +3976,19 @@
         <v>19</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G11" s="44"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>19</v>
@@ -4000,19 +3997,19 @@
         <v>19</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G12" s="44"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>19</v>
@@ -4021,40 +4018,40 @@
         <v>19</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G13" s="44"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="46" t="s">
+      <c r="E14" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="F14" s="46" t="s">
         <v>264</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>265</v>
       </c>
       <c r="G14" s="46"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B15" s="46" t="s">
         <v>19</v>
@@ -4063,19 +4060,19 @@
         <v>19</v>
       </c>
       <c r="D15" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="F15" s="46" t="s">
         <v>267</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>268</v>
       </c>
       <c r="G15" s="46"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B16" s="48" t="s">
         <v>19</v>
@@ -4084,21 +4081,21 @@
         <v>19</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F16" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="48" t="s">
         <v>331</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B17" s="48" t="s">
         <v>19</v>
@@ -4107,21 +4104,21 @@
         <v>19</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G17" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" s="48" t="s">
         <v>19</v>
@@ -4130,42 +4127,42 @@
         <v>19</v>
       </c>
       <c r="D18" s="48" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" s="48" t="s">
         <v>320</v>
       </c>
-      <c r="E18" s="48" t="s">
-        <v>321</v>
-      </c>
       <c r="F18" s="48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G18" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="46" t="s">
         <v>270</v>
       </c>
-      <c r="B19" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="46" t="s">
+      <c r="E19" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="46" t="s">
+      <c r="F19" s="46" t="s">
         <v>272</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>273</v>
       </c>
       <c r="G19" s="46"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>19</v>
@@ -4174,19 +4171,19 @@
         <v>19</v>
       </c>
       <c r="D20" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="F20" s="46" t="s">
         <v>275</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>276</v>
       </c>
       <c r="G20" s="46"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B21" s="47" t="s">
         <v>19</v>
@@ -4195,21 +4192,21 @@
         <v>19</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F21" s="47" t="s">
+        <v>328</v>
+      </c>
+      <c r="G21" s="47" t="s">
         <v>329</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>19</v>
@@ -4218,21 +4215,21 @@
         <v>19</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B23" s="47" t="s">
         <v>19</v>
@@ -4241,21 +4238,21 @@
         <v>19</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G23" s="47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" s="46" t="s">
         <v>19</v>
@@ -4267,18 +4264,18 @@
         <v>100</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G24" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>19</v>
@@ -4287,19 +4284,19 @@
         <v>19</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G25" s="46"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B26" s="46" t="s">
         <v>19</v>
@@ -4308,19 +4305,19 @@
         <v>19</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G26" s="46"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>19</v>
@@ -4329,19 +4326,19 @@
         <v>19</v>
       </c>
       <c r="D27" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="F27" s="46" t="s">
         <v>342</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="F27" s="46" t="s">
-        <v>344</v>
       </c>
       <c r="G27" s="46"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B28" s="46" t="s">
         <v>19</v>
@@ -4350,19 +4347,19 @@
         <v>19</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G28" s="46"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" s="46" t="s">
         <v>19</v>
@@ -4371,13 +4368,13 @@
         <v>19</v>
       </c>
       <c r="D29" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="F29" s="46" t="s">
         <v>348</v>
-      </c>
-      <c r="E29" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="F29" s="46" t="s">
-        <v>350</v>
       </c>
       <c r="G29" s="46"/>
     </row>
@@ -4393,11 +4390,11 @@
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="50" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="50" customWidth="1"/>
-    <col min="4" max="4" width="65.140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.7109375" style="50" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.85546875" style="50" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.7109375" style="50" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="71.5703125" style="50" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.5703125" style="51"/>
   </cols>
@@ -4407,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4415,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4465,30 +4462,30 @@
     </row>
     <row r="6" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>350</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="F6" s="55" t="s">
         <v>281</v>
       </c>
-      <c r="B6" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>352</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>351</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>282</v>
-      </c>
       <c r="G6" s="55" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B7" s="55" t="s">
         <v>19</v>
@@ -4497,67 +4494,67 @@
         <v>19</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="55" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>359</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>355</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>282</v>
-      </c>
       <c r="G8" s="55" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B9" s="55" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B10" s="54" t="s">
         <v>19</v>
@@ -4566,21 +4563,21 @@
         <v>19</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="54" t="s">
         <v>19</v>
@@ -4589,39 +4586,39 @@
         <v>19</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B12" s="54" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="D12" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>370</v>
+      </c>
+      <c r="F12" s="54" t="s">
         <v>367</v>
       </c>
-      <c r="E12" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>372</v>
-      </c>
       <c r="G12" s="54" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -4683,7 +4680,7 @@
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
       <c r="D5" s="38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E5" s="38"/>
       <c r="F5" s="38"/>
@@ -4694,7 +4691,7 @@
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
@@ -4705,7 +4702,7 @@
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
       <c r="D7" s="38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="38"/>
@@ -4716,7 +4713,7 @@
       <c r="B8" s="38"/>
       <c r="C8" s="38"/>
       <c r="D8" s="38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="38"/>
@@ -4727,7 +4724,7 @@
       <c r="B9" s="38"/>
       <c r="C9" s="38"/>
       <c r="D9" s="38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
